--- a/output/spreadsheet/pyg_inc_2026.xlsx
+++ b/output/spreadsheet/pyg_inc_2026.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="165" formatCode="0.00000000"/>
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,6 +55,11 @@
     </font>
     <font>
       <color rgb="00666666"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -127,9 +132,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -145,17 +150,19 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -531,7 +538,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -702,57 +709,57 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Actualizado: 11/07/2026 03:04 h</t>
+          <t>Shopify daily average | Actualizado: 31/07/2026 09:48 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="4" t="n"/>
       <c r="D3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)&lt;TODAY(),D5/DAY(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)),D5/MAX(NOW()-DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)&lt;TODAY(),D6/DAY(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)),D6/MAX(NOW()-DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)&lt;TODAY(),E5/DAY(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)),E5/MAX(NOW()-DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)&lt;TODAY(),E6/DAY(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)),E6/MAX(NOW()-DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="F3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)&lt;TODAY(),F5/DAY(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)),F5/MAX(NOW()-DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)&lt;TODAY(),F6/DAY(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)),F6/MAX(NOW()-DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="G3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)&lt;TODAY(),G5/DAY(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)),G5/MAX(NOW()-DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)&lt;TODAY(),G6/DAY(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)),G6/MAX(NOW()-DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)&lt;TODAY(),H5/DAY(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)),H5/MAX(NOW()-DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)&lt;TODAY(),H6/DAY(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)),H6/MAX(NOW()-DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)&lt;TODAY(),I5/DAY(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)),I5/MAX(NOW()-DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)&lt;TODAY(),I6/DAY(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)),I6/MAX(NOW()-DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="J3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)&lt;TODAY(),J5/DAY(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)),J5/MAX(NOW()-DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)&lt;TODAY(),J6/DAY(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)),J6/MAX(NOW()-DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="K3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)&lt;TODAY(),K5/DAY(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)),K5/MAX(NOW()-DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)&lt;TODAY(),K6/DAY(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)),K6/MAX(NOW()-DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="L3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)&lt;TODAY(),L5/DAY(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)),L5/MAX(NOW()-DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)&lt;TODAY(),L6/DAY(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)),L6/MAX(NOW()-DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="M3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)&lt;TODAY(),M5/DAY(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)),M5/MAX(NOW()-DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)&lt;TODAY(),M6/DAY(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)),M6/MAX(NOW()-DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="N3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)&lt;TODAY(),N5/DAY(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)),N5/MAX(NOW()-DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)&lt;TODAY(),N6/DAY(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)),N6/MAX(NOW()-DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="O3" s="4">
-        <f>IFERROR(IF(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)&lt;TODAY(),O5/DAY(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)),O5/MAX(NOW()-DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),1/24))),"")</f>
+        <f>IFERROR(IF(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)&lt;TODAY(),O6/DAY(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)),O6/MAX(NOW()-DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),1/24))),"")</f>
         <v/>
       </c>
       <c r="P3" s="4" t="n"/>
@@ -767,51 +774,51 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6">
-        <f>D5+D8+D9</f>
+        <f>D5+D9+D10</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>E5+E8+E9</f>
+        <f>E5+E9+E10</f>
         <v/>
       </c>
       <c r="F4" s="6">
-        <f>F5+F8+F9</f>
+        <f>F5+F9+F10</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>G5+G8+G9</f>
+        <f>G5+G9+G10</f>
         <v/>
       </c>
       <c r="H4" s="6">
-        <f>H5+H8+H9</f>
+        <f>H5+H9+H10</f>
         <v/>
       </c>
       <c r="I4" s="6">
-        <f>I5+I8+I9</f>
+        <f>I5+I9+I10</f>
         <v/>
       </c>
       <c r="J4" s="6">
-        <f>J5+J8+J9</f>
+        <f>J5+J9+J10</f>
         <v/>
       </c>
       <c r="K4" s="6">
-        <f>K5+K8+K9</f>
+        <f>K5+K9+K10</f>
         <v/>
       </c>
       <c r="L4" s="6">
-        <f>L5+L8+L9</f>
+        <f>L5+L9+L10</f>
         <v/>
       </c>
       <c r="M4" s="6">
-        <f>M5+M8+M9</f>
+        <f>M5+M9+M10</f>
         <v/>
       </c>
       <c r="N4" s="6">
-        <f>N5+N8+N9</f>
+        <f>N5+N9+N10</f>
         <v/>
       </c>
       <c r="O4" s="6">
-        <f>O5+O8+O9</f>
+        <f>O5+O9+O10</f>
         <v/>
       </c>
       <c r="P4" s="6">
@@ -891,51 +898,51 @@
       <c r="B6" s="10" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10">
-        <f>SUM(D7:D7)</f>
+        <f>D7</f>
         <v/>
       </c>
       <c r="E6" s="10">
-        <f>SUM(E7:E7)</f>
+        <f>E7</f>
         <v/>
       </c>
       <c r="F6" s="10">
-        <f>SUM(F7:F7)</f>
+        <f>F7</f>
         <v/>
       </c>
       <c r="G6" s="10">
-        <f>SUM(G7:G7)</f>
+        <f>G7</f>
         <v/>
       </c>
       <c r="H6" s="10">
-        <f>SUM(H7:H7)</f>
+        <f>H7</f>
         <v/>
       </c>
       <c r="I6" s="10">
-        <f>SUM(I7:I7)</f>
+        <f>I7</f>
         <v/>
       </c>
       <c r="J6" s="10">
-        <f>SUM(J7:J7)</f>
+        <f>J7</f>
         <v/>
       </c>
       <c r="K6" s="10">
-        <f>SUM(K7:K7)</f>
+        <f>K7</f>
         <v/>
       </c>
       <c r="L6" s="10">
-        <f>SUM(L7:L7)</f>
+        <f>L7</f>
         <v/>
       </c>
       <c r="M6" s="10">
-        <f>SUM(M7:M7)</f>
+        <f>M7</f>
         <v/>
       </c>
       <c r="N6" s="10">
-        <f>SUM(N7:N7)</f>
+        <f>N7</f>
         <v/>
       </c>
       <c r="O6" s="10">
-        <f>SUM(O7:O7)</f>
+        <f>O7</f>
         <v/>
       </c>
       <c r="P6" s="10">
@@ -1014,366 +1021,362 @@
         </is>
       </c>
     </row>
-    <row r="8" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="8" ht="12" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        avg/day</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)&lt;TODAY(),D7/DAY(EOMONTH(DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),0)),D7/MAX(NOW()-DATE(VALUE(LEFT(D$1,4)),VALUE(RIGHT(D$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="E8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)&lt;TODAY(),E7/DAY(EOMONTH(DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),0)),E7/MAX(NOW()-DATE(VALUE(LEFT(E$1,4)),VALUE(RIGHT(E$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)&lt;TODAY(),F7/DAY(EOMONTH(DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),0)),F7/MAX(NOW()-DATE(VALUE(LEFT(F$1,4)),VALUE(RIGHT(F$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="G8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)&lt;TODAY(),G7/DAY(EOMONTH(DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),0)),G7/MAX(NOW()-DATE(VALUE(LEFT(G$1,4)),VALUE(RIGHT(G$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)&lt;TODAY(),H7/DAY(EOMONTH(DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),0)),H7/MAX(NOW()-DATE(VALUE(LEFT(H$1,4)),VALUE(RIGHT(H$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="I8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)&lt;TODAY(),I7/DAY(EOMONTH(DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),0)),I7/MAX(NOW()-DATE(VALUE(LEFT(I$1,4)),VALUE(RIGHT(I$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="J8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)&lt;TODAY(),J7/DAY(EOMONTH(DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),0)),J7/MAX(NOW()-DATE(VALUE(LEFT(J$1,4)),VALUE(RIGHT(J$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)&lt;TODAY(),K7/DAY(EOMONTH(DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),0)),K7/MAX(NOW()-DATE(VALUE(LEFT(K$1,4)),VALUE(RIGHT(K$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)&lt;TODAY(),L7/DAY(EOMONTH(DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),0)),L7/MAX(NOW()-DATE(VALUE(LEFT(L$1,4)),VALUE(RIGHT(L$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)&lt;TODAY(),M7/DAY(EOMONTH(DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),0)),M7/MAX(NOW()-DATE(VALUE(LEFT(M$1,4)),VALUE(RIGHT(M$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)&lt;TODAY(),N7/DAY(EOMONTH(DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),0)),N7/MAX(NOW()-DATE(VALUE(LEFT(N$1,4)),VALUE(RIGHT(N$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>IFERROR(IF(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1)&gt;TODAY(),"",IF(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)&lt;TODAY(),O7/DAY(EOMONTH(DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),0)),O7/MAX(NOW()-DATE(VALUE(LEFT(O$1,4)),VALUE(RIGHT(O$1,2)),1),1/24))),"")</f>
+        <v/>
+      </c>
+      <c r="P8" s="12">
+        <f>SUM(D8:O8)</f>
+        <v/>
+      </c>
+      <c r="Q8" s="12" t="n"/>
+    </row>
+    <row r="9" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Services</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8">
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="E8" s="8">
+      <c r="E9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="F8" s="8">
+      <c r="F9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="G8" s="8">
+      <c r="G9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="H8" s="8">
+      <c r="H9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="I8" s="8">
+      <c r="I9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="J8" s="8">
+      <c r="J9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="K8" s="8">
+      <c r="K9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="L8" s="8">
+      <c r="L9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="M8" s="8">
+      <c r="M9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="N8" s="8">
+      <c r="N9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="O8" s="8">
+      <c r="O9" s="8">
         <f>0</f>
         <v/>
       </c>
-      <c r="P8" s="8">
-        <f>SUM(D8:O8)</f>
-        <v/>
-      </c>
-      <c r="Q8" s="8" t="n"/>
-    </row>
-    <row r="9" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="P9" s="8">
+        <f>SUM(D9:O9)</f>
+        <v/>
+      </c>
+      <c r="Q9" s="8" t="n"/>
+    </row>
+    <row r="10" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">  Uncategorized income</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
-      <c r="E9" s="10" t="n"/>
-      <c r="F9" s="10" t="n"/>
-      <c r="G9" s="10" t="n"/>
-      <c r="H9" s="10" t="n"/>
-      <c r="I9" s="10" t="n"/>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="10" t="n"/>
-      <c r="M9" s="10" t="n"/>
-      <c r="N9" s="10" t="n"/>
-      <c r="O9" s="10" t="n"/>
-      <c r="P9" s="10">
-        <f>SUM(D9:O9)</f>
-        <v/>
-      </c>
-      <c r="Q9" s="10" t="n"/>
-    </row>
-    <row r="10" ht="12" customHeight="1">
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4">
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="10" t="n"/>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="10" t="n"/>
+      <c r="J10" s="10" t="n"/>
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10">
         <f>SUM(D10:O10)</f>
         <v/>
       </c>
-      <c r="Q10" s="4" t="n"/>
+      <c r="Q10" s="10" t="n"/>
     </row>
     <row r="11" ht="12" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4">
+        <f>SUM(D11:O11)</f>
+        <v/>
+      </c>
+      <c r="Q11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="12" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6">
-        <f>D12+D32</f>
-        <v/>
-      </c>
-      <c r="E11" s="6">
-        <f>E12+E32</f>
-        <v/>
-      </c>
-      <c r="F11" s="6">
-        <f>F12+F32</f>
-        <v/>
-      </c>
-      <c r="G11" s="6">
-        <f>G12+G32</f>
-        <v/>
-      </c>
-      <c r="H11" s="6">
-        <f>H12+H32</f>
-        <v/>
-      </c>
-      <c r="I11" s="6">
-        <f>I12+I32</f>
-        <v/>
-      </c>
-      <c r="J11" s="6">
-        <f>J12+J32</f>
-        <v/>
-      </c>
-      <c r="K11" s="6">
-        <f>K12+K32</f>
-        <v/>
-      </c>
-      <c r="L11" s="6">
-        <f>L12+L32</f>
-        <v/>
-      </c>
-      <c r="M11" s="6">
-        <f>M12+M32</f>
-        <v/>
-      </c>
-      <c r="N11" s="6">
-        <f>N12+N32</f>
-        <v/>
-      </c>
-      <c r="O11" s="6">
-        <f>O12+O32</f>
-        <v/>
-      </c>
-      <c r="P11" s="6">
-        <f>SUM(D11:O11)</f>
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n"/>
-    </row>
-    <row r="12" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6">
+        <f>D13+D33</f>
+        <v/>
+      </c>
+      <c r="E12" s="6">
+        <f>E13+E33</f>
+        <v/>
+      </c>
+      <c r="F12" s="6">
+        <f>F13+F33</f>
+        <v/>
+      </c>
+      <c r="G12" s="6">
+        <f>G13+G33</f>
+        <v/>
+      </c>
+      <c r="H12" s="6">
+        <f>H13+H33</f>
+        <v/>
+      </c>
+      <c r="I12" s="6">
+        <f>I13+I33</f>
+        <v/>
+      </c>
+      <c r="J12" s="6">
+        <f>J13+J33</f>
+        <v/>
+      </c>
+      <c r="K12" s="6">
+        <f>K13+K33</f>
+        <v/>
+      </c>
+      <c r="L12" s="6">
+        <f>L13+L33</f>
+        <v/>
+      </c>
+      <c r="M12" s="6">
+        <f>M13+M33</f>
+        <v/>
+      </c>
+      <c r="N12" s="6">
+        <f>N13+N33</f>
+        <v/>
+      </c>
+      <c r="O12" s="6">
+        <f>O13+O33</f>
+        <v/>
+      </c>
+      <c r="P12" s="6">
+        <f>SUM(D12:O12)</f>
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n"/>
+    </row>
+    <row r="13" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  COGS</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8">
-        <f>D13+D18+D21</f>
-        <v/>
-      </c>
-      <c r="E12" s="8">
-        <f>E13+E18+E21</f>
-        <v/>
-      </c>
-      <c r="F12" s="8">
-        <f>F13+F18+F21</f>
-        <v/>
-      </c>
-      <c r="G12" s="8">
-        <f>G13+G18+G21</f>
-        <v/>
-      </c>
-      <c r="H12" s="8">
-        <f>H13+H18+H21</f>
-        <v/>
-      </c>
-      <c r="I12" s="8">
-        <f>I13+I18+I21</f>
-        <v/>
-      </c>
-      <c r="J12" s="8">
-        <f>J13+J18+J21</f>
-        <v/>
-      </c>
-      <c r="K12" s="8">
-        <f>K13+K18+K21</f>
-        <v/>
-      </c>
-      <c r="L12" s="8">
-        <f>L13+L18+L21</f>
-        <v/>
-      </c>
-      <c r="M12" s="8">
-        <f>M13+M18+M21</f>
-        <v/>
-      </c>
-      <c r="N12" s="8">
-        <f>N13+N18+N21</f>
-        <v/>
-      </c>
-      <c r="O12" s="8">
-        <f>O13+O18+O21</f>
-        <v/>
-      </c>
-      <c r="P12" s="8">
-        <f>SUM(D12:O12)</f>
-        <v/>
-      </c>
-      <c r="Q12" s="8" t="n"/>
-    </row>
-    <row r="13" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8">
+        <f>D14+D19+D22</f>
+        <v/>
+      </c>
+      <c r="E13" s="8">
+        <f>E14+E19+E22</f>
+        <v/>
+      </c>
+      <c r="F13" s="8">
+        <f>F14+F19+F22</f>
+        <v/>
+      </c>
+      <c r="G13" s="8">
+        <f>G14+G19+G22</f>
+        <v/>
+      </c>
+      <c r="H13" s="8">
+        <f>H14+H19+H22</f>
+        <v/>
+      </c>
+      <c r="I13" s="8">
+        <f>I14+I19+I22</f>
+        <v/>
+      </c>
+      <c r="J13" s="8">
+        <f>J14+J19+J22</f>
+        <v/>
+      </c>
+      <c r="K13" s="8">
+        <f>K14+K19+K22</f>
+        <v/>
+      </c>
+      <c r="L13" s="8">
+        <f>L14+L19+L22</f>
+        <v/>
+      </c>
+      <c r="M13" s="8">
+        <f>M14+M19+M22</f>
+        <v/>
+      </c>
+      <c r="N13" s="8">
+        <f>N14+N19+N22</f>
+        <v/>
+      </c>
+      <c r="O13" s="8">
+        <f>O14+O19+O22</f>
+        <v/>
+      </c>
+      <c r="P13" s="8">
+        <f>SUM(D13:O13)</f>
+        <v/>
+      </c>
+      <c r="Q13" s="8" t="n"/>
+    </row>
+    <row r="14" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Manufacturing</t>
         </is>
       </c>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10">
-        <f>SUM(D14:D15)+D16</f>
-        <v/>
-      </c>
-      <c r="E13" s="10">
-        <f>SUM(E14:E15)+E16</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>SUM(F14:F15)+F16</f>
-        <v/>
-      </c>
-      <c r="G13" s="10">
-        <f>SUM(G14:G15)+G16</f>
-        <v/>
-      </c>
-      <c r="H13" s="10">
-        <f>SUM(H14:H15)+H16</f>
-        <v/>
-      </c>
-      <c r="I13" s="10">
-        <f>SUM(I14:I15)+I16</f>
-        <v/>
-      </c>
-      <c r="J13" s="10">
-        <f>SUM(J14:J15)+J16</f>
-        <v/>
-      </c>
-      <c r="K13" s="10">
-        <f>SUM(K14:K15)+K16</f>
-        <v/>
-      </c>
-      <c r="L13" s="10">
-        <f>SUM(L14:L15)+L16</f>
-        <v/>
-      </c>
-      <c r="M13" s="10">
-        <f>SUM(M14:M15)+M16</f>
-        <v/>
-      </c>
-      <c r="N13" s="10">
-        <f>SUM(N14:N15)+N16</f>
-        <v/>
-      </c>
-      <c r="O13" s="10">
-        <f>SUM(O14:O15)+O16</f>
-        <v/>
-      </c>
-      <c r="P13" s="10">
-        <f>SUM(D13:O13)</f>
-        <v/>
-      </c>
-      <c r="Q13" s="10" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      JONDO</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="E14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="F14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="H14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="I14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="J14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="K14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="L14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="M14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="N14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="O14" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A14))</f>
-        <v/>
-      </c>
-      <c r="P14" s="4">
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10">
+        <f>SUM(D15:D16)+D17</f>
+        <v/>
+      </c>
+      <c r="E14" s="10">
+        <f>SUM(E15:E16)+E17</f>
+        <v/>
+      </c>
+      <c r="F14" s="10">
+        <f>SUM(F15:F16)+F17</f>
+        <v/>
+      </c>
+      <c r="G14" s="10">
+        <f>SUM(G15:G16)+G17</f>
+        <v/>
+      </c>
+      <c r="H14" s="10">
+        <f>SUM(H15:H16)+H17</f>
+        <v/>
+      </c>
+      <c r="I14" s="10">
+        <f>SUM(I15:I16)+I17</f>
+        <v/>
+      </c>
+      <c r="J14" s="10">
+        <f>SUM(J15:J16)+J17</f>
+        <v/>
+      </c>
+      <c r="K14" s="10">
+        <f>SUM(K15:K16)+K17</f>
+        <v/>
+      </c>
+      <c r="L14" s="10">
+        <f>SUM(L15:L16)+L17</f>
+        <v/>
+      </c>
+      <c r="M14" s="10">
+        <f>SUM(M15:M16)+M17</f>
+        <v/>
+      </c>
+      <c r="N14" s="10">
+        <f>SUM(N15:N16)+N17</f>
+        <v/>
+      </c>
+      <c r="O14" s="10">
+        <f>SUM(O15:O16)+O17</f>
+        <v/>
+      </c>
+      <c r="P14" s="10">
         <f>SUM(D14:O14)</f>
         <v/>
       </c>
-      <c r="Q14" s="4" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -1382,7 +1385,7 @@
     <row r="15" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">      TGI</t>
+          <t xml:space="preserve">      JONDO</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -1439,483 +1442,528 @@
         <f>SUM(D15:O15)</f>
         <v/>
       </c>
-      <c r="Q15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="12" customHeight="1">
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">      Consumo marcos</t>
+          <t xml:space="preserve">      TGI</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n">
-        <v>2658.96</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>1470.37</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>1496.84</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>899.95</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>730.88</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>921.26</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>113.84</v>
-      </c>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
+      <c r="D16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="F16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="H16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="I16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="J16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="K16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="L16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="M16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="N16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
+      <c r="O16" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"manufacturing",'g-expenses-inc'!$E:$E,TRIM($A16))</f>
+        <v/>
+      </c>
       <c r="P16" s="4">
         <f>SUM(D16:O16)</f>
         <v/>
       </c>
       <c r="Q16" s="4" t="n"/>
     </row>
-    <row r="17" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="17" ht="12" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      Consumo marcos</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n">
+        <v>2658.96</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>1470.37</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1496.84</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>899.95</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>730.88</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>921.26</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>434.04</v>
+      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4">
+        <f>SUM(D17:O17)</f>
+        <v/>
+      </c>
+      <c r="Q17" s="4" t="n"/>
+    </row>
+    <row r="18" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Manufacturing / sales</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11">
-        <f>IFERROR(D13/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E17" s="11">
-        <f>IFERROR(E13/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="11">
-        <f>IFERROR(F13/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G17" s="11">
-        <f>IFERROR(G13/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H17" s="11">
-        <f>IFERROR(H13/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="11">
-        <f>IFERROR(I13/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="11">
-        <f>IFERROR(J13/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K17" s="11">
-        <f>IFERROR(K13/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L17" s="11">
-        <f>IFERROR(L13/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M17" s="11">
-        <f>IFERROR(M13/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N17" s="11">
-        <f>IFERROR(N13/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O17" s="11">
-        <f>IFERROR(O13/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P17" s="11">
-        <f>IFERROR(P13/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q17" s="11" t="n"/>
-    </row>
-    <row r="18" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="B18" s="13" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="13">
+        <f>IFERROR(D14/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E18" s="13">
+        <f>IFERROR(E14/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="13">
+        <f>IFERROR(F14/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G18" s="13">
+        <f>IFERROR(G14/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="13">
+        <f>IFERROR(H14/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I18" s="13">
+        <f>IFERROR(I14/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J18" s="13">
+        <f>IFERROR(J14/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K18" s="13">
+        <f>IFERROR(K14/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L18" s="13">
+        <f>IFERROR(L14/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M18" s="13">
+        <f>IFERROR(M14/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N18" s="13">
+        <f>IFERROR(N14/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O18" s="13">
+        <f>IFERROR(O14/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P18" s="13">
+        <f>IFERROR(P14/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q18" s="13" t="n"/>
+    </row>
+    <row r="19" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Logistics</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10">
-        <f>SUM(D19:D19)</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>SUM(E19:E19)</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
-        <f>SUM(F19:F19)</f>
-        <v/>
-      </c>
-      <c r="G18" s="10">
-        <f>SUM(G19:G19)</f>
-        <v/>
-      </c>
-      <c r="H18" s="10">
-        <f>SUM(H19:H19)</f>
-        <v/>
-      </c>
-      <c r="I18" s="10">
-        <f>SUM(I19:I19)</f>
-        <v/>
-      </c>
-      <c r="J18" s="10">
-        <f>SUM(J19:J19)</f>
-        <v/>
-      </c>
-      <c r="K18" s="10">
-        <f>SUM(K19:K19)</f>
-        <v/>
-      </c>
-      <c r="L18" s="10">
-        <f>SUM(L19:L19)</f>
-        <v/>
-      </c>
-      <c r="M18" s="10">
-        <f>SUM(M19:M19)</f>
-        <v/>
-      </c>
-      <c r="N18" s="10">
-        <f>SUM(N19:N19)</f>
-        <v/>
-      </c>
-      <c r="O18" s="10">
-        <f>SUM(O19:O19)</f>
-        <v/>
-      </c>
-      <c r="P18" s="10">
-        <f>SUM(D18:O18)</f>
-        <v/>
-      </c>
-      <c r="Q18" s="10" t="inlineStr">
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10">
+        <f>SUM(D20:D20)</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>SUM(E20:E20)</f>
+        <v/>
+      </c>
+      <c r="F19" s="10">
+        <f>SUM(F20:F20)</f>
+        <v/>
+      </c>
+      <c r="G19" s="10">
+        <f>SUM(G20:G20)</f>
+        <v/>
+      </c>
+      <c r="H19" s="10">
+        <f>SUM(H20:H20)</f>
+        <v/>
+      </c>
+      <c r="I19" s="10">
+        <f>SUM(I20:I20)</f>
+        <v/>
+      </c>
+      <c r="J19" s="10">
+        <f>SUM(J20:J20)</f>
+        <v/>
+      </c>
+      <c r="K19" s="10">
+        <f>SUM(K20:K20)</f>
+        <v/>
+      </c>
+      <c r="L19" s="10">
+        <f>SUM(L20:L20)</f>
+        <v/>
+      </c>
+      <c r="M19" s="10">
+        <f>SUM(M20:M20)</f>
+        <v/>
+      </c>
+      <c r="N19" s="10">
+        <f>SUM(N20:N20)</f>
+        <v/>
+      </c>
+      <c r="O19" s="10">
+        <f>SUM(O20:O20)</f>
+        <v/>
+      </c>
+      <c r="P19" s="10">
+        <f>SUM(D19:O19)</f>
+        <v/>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="19" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve">      TGI</t>
         </is>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="E19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="F19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="G19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="H19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="I19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="J19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="K19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="L19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="M19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="N19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="O19" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A19))</f>
-        <v/>
-      </c>
-      <c r="P19" s="4">
-        <f>SUM(D19:O19)</f>
-        <v/>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="E20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="F20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="H20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="I20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="J20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="K20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="L20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="M20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="N20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="O20" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"logistics",'g-expenses-inc'!$E:$E,TRIM($A20))</f>
+        <v/>
+      </c>
+      <c r="P20" s="4">
+        <f>SUM(D20:O20)</f>
+        <v/>
+      </c>
+      <c r="Q20" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="20" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Logistics / sales</t>
         </is>
       </c>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11">
-        <f>IFERROR(D18/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E20" s="11">
-        <f>IFERROR(E18/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F20" s="11">
-        <f>IFERROR(F18/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G20" s="11">
-        <f>IFERROR(G18/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H20" s="11">
-        <f>IFERROR(H18/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="11">
-        <f>IFERROR(I18/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="11">
-        <f>IFERROR(J18/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K20" s="11">
-        <f>IFERROR(K18/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L20" s="11">
-        <f>IFERROR(L18/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="11">
-        <f>IFERROR(M18/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N20" s="11">
-        <f>IFERROR(N18/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O20" s="11">
-        <f>IFERROR(O18/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P20" s="11">
-        <f>IFERROR(P18/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q20" s="11" t="n"/>
-    </row>
-    <row r="21" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13">
+        <f>IFERROR(D19/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E21" s="13">
+        <f>IFERROR(E19/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="13">
+        <f>IFERROR(F19/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G21" s="13">
+        <f>IFERROR(G19/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="13">
+        <f>IFERROR(H19/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I21" s="13">
+        <f>IFERROR(I19/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J21" s="13">
+        <f>IFERROR(J19/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K21" s="13">
+        <f>IFERROR(K19/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L21" s="13">
+        <f>IFERROR(L19/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="13">
+        <f>IFERROR(M19/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N21" s="13">
+        <f>IFERROR(N19/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O21" s="13">
+        <f>IFERROR(O19/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P21" s="13">
+        <f>IFERROR(P19/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="13" t="n"/>
+    </row>
+    <row r="22" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Payment fees</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10">
-        <f>SUM(D22:D22)</f>
-        <v/>
-      </c>
-      <c r="E21" s="10">
-        <f>SUM(E22:E22)</f>
-        <v/>
-      </c>
-      <c r="F21" s="10">
-        <f>SUM(F22:F22)</f>
-        <v/>
-      </c>
-      <c r="G21" s="10">
-        <f>SUM(G22:G22)</f>
-        <v/>
-      </c>
-      <c r="H21" s="10">
-        <f>SUM(H22:H22)</f>
-        <v/>
-      </c>
-      <c r="I21" s="10">
-        <f>SUM(I22:I22)</f>
-        <v/>
-      </c>
-      <c r="J21" s="10">
-        <f>SUM(J22:J22)</f>
-        <v/>
-      </c>
-      <c r="K21" s="10">
-        <f>SUM(K22:K22)</f>
-        <v/>
-      </c>
-      <c r="L21" s="10">
-        <f>SUM(L22:L22)</f>
-        <v/>
-      </c>
-      <c r="M21" s="10">
-        <f>SUM(M22:M22)</f>
-        <v/>
-      </c>
-      <c r="N21" s="10">
-        <f>SUM(N22:N22)</f>
-        <v/>
-      </c>
-      <c r="O21" s="10">
-        <f>SUM(O22:O22)</f>
-        <v/>
-      </c>
-      <c r="P21" s="10">
-        <f>SUM(D21:O21)</f>
-        <v/>
-      </c>
-      <c r="Q21" s="10" t="inlineStr">
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10">
+        <f>SUM(D23:D23)</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>SUM(E23:E23)</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>SUM(F23:F23)</f>
+        <v/>
+      </c>
+      <c r="G22" s="10">
+        <f>SUM(G23:G23)</f>
+        <v/>
+      </c>
+      <c r="H22" s="10">
+        <f>SUM(H23:H23)</f>
+        <v/>
+      </c>
+      <c r="I22" s="10">
+        <f>SUM(I23:I23)</f>
+        <v/>
+      </c>
+      <c r="J22" s="10">
+        <f>SUM(J23:J23)</f>
+        <v/>
+      </c>
+      <c r="K22" s="10">
+        <f>SUM(K23:K23)</f>
+        <v/>
+      </c>
+      <c r="L22" s="10">
+        <f>SUM(L23:L23)</f>
+        <v/>
+      </c>
+      <c r="M22" s="10">
+        <f>SUM(M23:M23)</f>
+        <v/>
+      </c>
+      <c r="N22" s="10">
+        <f>SUM(N23:N23)</f>
+        <v/>
+      </c>
+      <c r="O22" s="10">
+        <f>SUM(O23:O23)</f>
+        <v/>
+      </c>
+      <c r="P22" s="10">
+        <f>SUM(D22:O22)</f>
+        <v/>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="22" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A22" t="inlineStr">
+    <row r="23" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">      SHOPIFY</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,D$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="E22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,E$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="F22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,F$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="G22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,G$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="H22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,H$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="I22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,I$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="J22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,J$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="K22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,K$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="L22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,L$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="M22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,M$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="N22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,N$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="O22" s="4">
-        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,O$1,'g-payment-fees-inc'!$C:$C,TRIM($A22))</f>
-        <v/>
-      </c>
-      <c r="P22" s="4">
-        <f>SUM(D22:O22)</f>
-        <v/>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="12" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Royalties</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
       <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n">
-        <v>561.38</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>878.29</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>852</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>663.5</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>548.4299999999999</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>618.6900000000001</v>
-      </c>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
+      <c r="D23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,D$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="E23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,E$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="F23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,F$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,G$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="H23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,H$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="I23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,I$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="J23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,J$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="K23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,K$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="L23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,L$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="M23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,M$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="N23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,N$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
+      <c r="O23" s="4">
+        <f>SUMIFS('g-payment-fees-inc'!$H:$H,'g-payment-fees-inc'!$A:$A,O$1,'g-payment-fees-inc'!$C:$C,TRIM($A23))</f>
+        <v/>
+      </c>
       <c r="P23" s="4">
         <f>SUM(D23:O23)</f>
         <v/>
       </c>
-      <c r="Q23" s="4" t="n"/>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="12" customHeight="1">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Royalties</t>
+        </is>
+      </c>
       <c r="B24" s="4" t="n"/>
       <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
+      <c r="D24" s="4" t="n">
+        <v>561.38</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>878.29</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>852</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>663.5</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>548.4299999999999</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>618.6900000000001</v>
+      </c>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
@@ -1928,679 +1976,634 @@
       </c>
       <c r="Q24" s="4" t="n"/>
     </row>
-    <row r="25" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25" ht="12" customHeight="1">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4">
+        <f>SUM(D25:O25)</f>
+        <v/>
+      </c>
+      <c r="Q25" s="4" t="n"/>
+    </row>
+    <row r="26" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">    % Payment fees / sales</t>
         </is>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11">
-        <f>IFERROR(D21/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E25" s="11">
-        <f>IFERROR(E21/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F25" s="11">
-        <f>IFERROR(F21/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G25" s="11">
-        <f>IFERROR(G21/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H25" s="11">
-        <f>IFERROR(H21/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I25" s="11">
-        <f>IFERROR(I21/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="11">
-        <f>IFERROR(J21/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K25" s="11">
-        <f>IFERROR(K21/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L25" s="11">
-        <f>IFERROR(L21/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M25" s="11">
-        <f>IFERROR(M21/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N25" s="11">
-        <f>IFERROR(N21/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O25" s="11">
-        <f>IFERROR(O21/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P25" s="11">
-        <f>IFERROR(P21/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q25" s="11" t="n"/>
-    </row>
-    <row r="26" ht="12" customHeight="1">
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
-      <c r="O26" s="4" t="n"/>
-      <c r="P26" s="4">
-        <f>SUM(D26:O26)</f>
-        <v/>
-      </c>
-      <c r="Q26" s="4" t="n"/>
+      <c r="B26" s="13" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="13">
+        <f>IFERROR(D22/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E26" s="13">
+        <f>IFERROR(E22/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="13">
+        <f>IFERROR(F22/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G26" s="13">
+        <f>IFERROR(G22/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="13">
+        <f>IFERROR(H22/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I26" s="13">
+        <f>IFERROR(I22/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J26" s="13">
+        <f>IFERROR(J22/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K26" s="13">
+        <f>IFERROR(K22/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L26" s="13">
+        <f>IFERROR(L22/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="13">
+        <f>IFERROR(M22/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N26" s="13">
+        <f>IFERROR(N22/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O26" s="13">
+        <f>IFERROR(O22/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P26" s="13">
+        <f>IFERROR(P22/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q26" s="13" t="n"/>
     </row>
     <row r="27" ht="12" customHeight="1">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4">
+        <f>SUM(D27:O27)</f>
+        <v/>
+      </c>
+      <c r="Q27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="12" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>GROSS MARGIN (SALES-MANUFACTURING)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="14" t="n"/>
-      <c r="D27" s="14">
-        <f>D5-D13</f>
-        <v/>
-      </c>
-      <c r="E27" s="14">
-        <f>E5-E13</f>
-        <v/>
-      </c>
-      <c r="F27" s="14">
-        <f>F5-F13</f>
-        <v/>
-      </c>
-      <c r="G27" s="14">
-        <f>G5-G13</f>
-        <v/>
-      </c>
-      <c r="H27" s="14">
-        <f>H5-H13</f>
-        <v/>
-      </c>
-      <c r="I27" s="14">
-        <f>I5-I13</f>
-        <v/>
-      </c>
-      <c r="J27" s="14">
-        <f>J5-J13</f>
-        <v/>
-      </c>
-      <c r="K27" s="14">
-        <f>K5-K13</f>
-        <v/>
-      </c>
-      <c r="L27" s="14">
-        <f>L5-L13</f>
-        <v/>
-      </c>
-      <c r="M27" s="14">
-        <f>M5-M13</f>
-        <v/>
-      </c>
-      <c r="N27" s="14">
-        <f>N5-N13</f>
-        <v/>
-      </c>
-      <c r="O27" s="14">
-        <f>O5-O13</f>
-        <v/>
-      </c>
-      <c r="P27" s="14">
-        <f>SUM(D27:O27)</f>
-        <v/>
-      </c>
-      <c r="Q27" s="14" t="n"/>
-    </row>
-    <row r="28" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16">
+        <f>D5-D14</f>
+        <v/>
+      </c>
+      <c r="E28" s="16">
+        <f>E5-E14</f>
+        <v/>
+      </c>
+      <c r="F28" s="16">
+        <f>F5-F14</f>
+        <v/>
+      </c>
+      <c r="G28" s="16">
+        <f>G5-G14</f>
+        <v/>
+      </c>
+      <c r="H28" s="16">
+        <f>H5-H14</f>
+        <v/>
+      </c>
+      <c r="I28" s="16">
+        <f>I5-I14</f>
+        <v/>
+      </c>
+      <c r="J28" s="16">
+        <f>J5-J14</f>
+        <v/>
+      </c>
+      <c r="K28" s="16">
+        <f>K5-K14</f>
+        <v/>
+      </c>
+      <c r="L28" s="16">
+        <f>L5-L14</f>
+        <v/>
+      </c>
+      <c r="M28" s="16">
+        <f>M5-M14</f>
+        <v/>
+      </c>
+      <c r="N28" s="16">
+        <f>N5-N14</f>
+        <v/>
+      </c>
+      <c r="O28" s="16">
+        <f>O5-O14</f>
+        <v/>
+      </c>
+      <c r="P28" s="16">
+        <f>SUM(D28:O28)</f>
+        <v/>
+      </c>
+      <c r="Q28" s="16" t="n"/>
+    </row>
+    <row r="29" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>% gross margin</t>
         </is>
       </c>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11">
-        <f>IFERROR(D27/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E28" s="11">
-        <f>IFERROR(E27/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F28" s="11">
-        <f>IFERROR(F27/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="11">
-        <f>IFERROR(G27/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="11">
-        <f>IFERROR(H27/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I28" s="11">
-        <f>IFERROR(I27/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="11">
-        <f>IFERROR(J27/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K28" s="11">
-        <f>IFERROR(K27/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L28" s="11">
-        <f>IFERROR(L27/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M28" s="11">
-        <f>IFERROR(M27/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N28" s="11">
-        <f>IFERROR(N27/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O28" s="11">
-        <f>IFERROR(O27/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P28" s="11">
-        <f>IFERROR(P27/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="12" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="B29" s="13" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="13">
+        <f>IFERROR(D28/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E29" s="13">
+        <f>IFERROR(E28/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F29" s="13">
+        <f>IFERROR(F28/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="13">
+        <f>IFERROR(G28/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="13">
+        <f>IFERROR(H28/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I29" s="13">
+        <f>IFERROR(I28/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J29" s="13">
+        <f>IFERROR(J28/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K29" s="13">
+        <f>IFERROR(K28/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L29" s="13">
+        <f>IFERROR(L28/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="13">
+        <f>IFERROR(M28/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N29" s="13">
+        <f>IFERROR(N28/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O29" s="13">
+        <f>IFERROR(O28/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P29" s="13">
+        <f>IFERROR(P28/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="13" t="n"/>
+    </row>
+    <row r="30" ht="12" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>Contributive margin (product sales-COGS)</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14">
-        <f>D5-D12-D23</f>
-        <v/>
-      </c>
-      <c r="E29" s="14">
-        <f>E5-E12-E23</f>
-        <v/>
-      </c>
-      <c r="F29" s="14">
-        <f>F5-F12-F23</f>
-        <v/>
-      </c>
-      <c r="G29" s="14">
-        <f>G5-G12-G23</f>
-        <v/>
-      </c>
-      <c r="H29" s="14">
-        <f>H5-H12-H23</f>
-        <v/>
-      </c>
-      <c r="I29" s="14">
-        <f>I5-I12-I23</f>
-        <v/>
-      </c>
-      <c r="J29" s="14">
-        <f>J5-J12-J23</f>
-        <v/>
-      </c>
-      <c r="K29" s="14">
-        <f>K5-K12-K23</f>
-        <v/>
-      </c>
-      <c r="L29" s="14">
-        <f>L5-L12-L23</f>
-        <v/>
-      </c>
-      <c r="M29" s="14">
-        <f>M5-M12-M23</f>
-        <v/>
-      </c>
-      <c r="N29" s="14">
-        <f>N5-N12-N23</f>
-        <v/>
-      </c>
-      <c r="O29" s="14">
-        <f>O5-O12-O23</f>
-        <v/>
-      </c>
-      <c r="P29" s="14">
-        <f>SUM(D29:O29)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="14" t="n"/>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16">
+        <f>D5-D13-D24</f>
+        <v/>
+      </c>
+      <c r="E30" s="16">
+        <f>E5-E13-E24</f>
+        <v/>
+      </c>
+      <c r="F30" s="16">
+        <f>F5-F13-F24</f>
+        <v/>
+      </c>
+      <c r="G30" s="16">
+        <f>G5-G13-G24</f>
+        <v/>
+      </c>
+      <c r="H30" s="16">
+        <f>H5-H13-H24</f>
+        <v/>
+      </c>
+      <c r="I30" s="16">
+        <f>I5-I13-I24</f>
+        <v/>
+      </c>
+      <c r="J30" s="16">
+        <f>J5-J13-J24</f>
+        <v/>
+      </c>
+      <c r="K30" s="16">
+        <f>K5-K13-K24</f>
+        <v/>
+      </c>
+      <c r="L30" s="16">
+        <f>L5-L13-L24</f>
+        <v/>
+      </c>
+      <c r="M30" s="16">
+        <f>M5-M13-M24</f>
+        <v/>
+      </c>
+      <c r="N30" s="16">
+        <f>N5-N13-N24</f>
+        <v/>
+      </c>
+      <c r="O30" s="16">
+        <f>O5-O13-O24</f>
+        <v/>
+      </c>
+      <c r="P30" s="16">
+        <f>SUM(D30:O30)</f>
+        <v/>
+      </c>
+      <c r="Q30" s="16" t="n"/>
+    </row>
+    <row r="31" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>% contributive margin</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11">
-        <f>IFERROR(D29/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E30" s="11">
-        <f>IFERROR(E29/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F30" s="11">
-        <f>IFERROR(F29/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G30" s="11">
-        <f>IFERROR(G29/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H30" s="11">
-        <f>IFERROR(H29/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I30" s="11">
-        <f>IFERROR(I29/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J30" s="11">
-        <f>IFERROR(J29/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K30" s="11">
-        <f>IFERROR(K29/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L30" s="11">
-        <f>IFERROR(L29/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M30" s="11">
-        <f>IFERROR(M29/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N30" s="11">
-        <f>IFERROR(N29/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O30" s="11">
-        <f>IFERROR(O29/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P30" s="11">
-        <f>IFERROR(P29/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q30" s="11" t="n"/>
-    </row>
-    <row r="31" ht="12" customHeight="1">
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4">
-        <f>SUM(D31:O31)</f>
-        <v/>
-      </c>
-      <c r="Q31" s="4" t="n"/>
-    </row>
-    <row r="32" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A32" s="7" t="inlineStr">
+      <c r="B31" s="13" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="13">
+        <f>IFERROR(D30/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E31" s="13">
+        <f>IFERROR(E30/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F31" s="13">
+        <f>IFERROR(F30/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="13">
+        <f>IFERROR(G30/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="13">
+        <f>IFERROR(H30/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I31" s="13">
+        <f>IFERROR(I30/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J31" s="13">
+        <f>IFERROR(J30/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K31" s="13">
+        <f>IFERROR(K30/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L31" s="13">
+        <f>IFERROR(L30/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="13">
+        <f>IFERROR(M30/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N31" s="13">
+        <f>IFERROR(N30/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O31" s="13">
+        <f>IFERROR(O30/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P31" s="13">
+        <f>IFERROR(P30/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q31" s="13" t="n"/>
+    </row>
+    <row r="32" ht="12" customHeight="1">
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4">
+        <f>SUM(D32:O32)</f>
+        <v/>
+      </c>
+      <c r="Q32" s="4" t="n"/>
+    </row>
+    <row r="33" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Opex</t>
         </is>
       </c>
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8">
-        <f>D33+D35+D42+D44</f>
-        <v/>
-      </c>
-      <c r="E32" s="8">
-        <f>E33+E35+E42+E44</f>
-        <v/>
-      </c>
-      <c r="F32" s="8">
-        <f>F33+F35+F42+F44</f>
-        <v/>
-      </c>
-      <c r="G32" s="8">
-        <f>G33+G35+G42+G44</f>
-        <v/>
-      </c>
-      <c r="H32" s="8">
-        <f>H33+H35+H42+H44</f>
-        <v/>
-      </c>
-      <c r="I32" s="8">
-        <f>I33+I35+I42+I44</f>
-        <v/>
-      </c>
-      <c r="J32" s="8">
-        <f>J33+J35+J42+J44</f>
-        <v/>
-      </c>
-      <c r="K32" s="8">
-        <f>K33+K35+K42+K44</f>
-        <v/>
-      </c>
-      <c r="L32" s="8">
-        <f>L33+L35+L42+L44</f>
-        <v/>
-      </c>
-      <c r="M32" s="8">
-        <f>M33+M35+M42+M44</f>
-        <v/>
-      </c>
-      <c r="N32" s="8">
-        <f>N33+N35+N42+N44</f>
-        <v/>
-      </c>
-      <c r="O32" s="8">
-        <f>O33+O35+O42+O44</f>
-        <v/>
-      </c>
-      <c r="P32" s="8">
-        <f>SUM(D32:O32)</f>
-        <v/>
-      </c>
-      <c r="Q32" s="8" t="n"/>
-    </row>
-    <row r="33" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="B33" s="8" t="n"/>
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8">
+        <f>D34+D36+D43+D45</f>
+        <v/>
+      </c>
+      <c r="E33" s="8">
+        <f>E34+E36+E43+E45</f>
+        <v/>
+      </c>
+      <c r="F33" s="8">
+        <f>F34+F36+F43+F45</f>
+        <v/>
+      </c>
+      <c r="G33" s="8">
+        <f>G34+G36+G43+G45</f>
+        <v/>
+      </c>
+      <c r="H33" s="8">
+        <f>H34+H36+H43+H45</f>
+        <v/>
+      </c>
+      <c r="I33" s="8">
+        <f>I34+I36+I43+I45</f>
+        <v/>
+      </c>
+      <c r="J33" s="8">
+        <f>J34+J36+J43+J45</f>
+        <v/>
+      </c>
+      <c r="K33" s="8">
+        <f>K34+K36+K43+K45</f>
+        <v/>
+      </c>
+      <c r="L33" s="8">
+        <f>L34+L36+L43+L45</f>
+        <v/>
+      </c>
+      <c r="M33" s="8">
+        <f>M34+M36+M43+M45</f>
+        <v/>
+      </c>
+      <c r="N33" s="8">
+        <f>N34+N36+N43+N45</f>
+        <v/>
+      </c>
+      <c r="O33" s="8">
+        <f>O34+O36+O43+O45</f>
+        <v/>
+      </c>
+      <c r="P33" s="8">
+        <f>SUM(D33:O33)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="8" t="n"/>
+    </row>
+    <row r="34" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Shared services</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10">
-        <f>SUM(D34:D34)</f>
-        <v/>
-      </c>
-      <c r="E33" s="10">
-        <f>SUM(E34:E34)</f>
-        <v/>
-      </c>
-      <c r="F33" s="10">
-        <f>SUM(F34:F34)</f>
-        <v/>
-      </c>
-      <c r="G33" s="10">
-        <f>SUM(G34:G34)</f>
-        <v/>
-      </c>
-      <c r="H33" s="10">
-        <f>SUM(H34:H34)</f>
-        <v/>
-      </c>
-      <c r="I33" s="10">
-        <f>SUM(I34:I34)</f>
-        <v/>
-      </c>
-      <c r="J33" s="10">
-        <f>SUM(J34:J34)</f>
-        <v/>
-      </c>
-      <c r="K33" s="10">
-        <f>SUM(K34:K34)</f>
-        <v/>
-      </c>
-      <c r="L33" s="10">
-        <f>SUM(L34:L34)</f>
-        <v/>
-      </c>
-      <c r="M33" s="10">
-        <f>SUM(M34:M34)</f>
-        <v/>
-      </c>
-      <c r="N33" s="10">
-        <f>SUM(N34:N34)</f>
-        <v/>
-      </c>
-      <c r="O33" s="10">
-        <f>SUM(O34:O34)</f>
-        <v/>
-      </c>
-      <c r="P33" s="10">
-        <f>SUM(D33:O33)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="10" t="inlineStr">
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10">
+        <f>SUM(D35:D35)</f>
+        <v/>
+      </c>
+      <c r="E34" s="10">
+        <f>SUM(E35:E35)</f>
+        <v/>
+      </c>
+      <c r="F34" s="10">
+        <f>SUM(F35:F35)</f>
+        <v/>
+      </c>
+      <c r="G34" s="10">
+        <f>SUM(G35:G35)</f>
+        <v/>
+      </c>
+      <c r="H34" s="10">
+        <f>SUM(H35:H35)</f>
+        <v/>
+      </c>
+      <c r="I34" s="10">
+        <f>SUM(I35:I35)</f>
+        <v/>
+      </c>
+      <c r="J34" s="10">
+        <f>SUM(J35:J35)</f>
+        <v/>
+      </c>
+      <c r="K34" s="10">
+        <f>SUM(K35:K35)</f>
+        <v/>
+      </c>
+      <c r="L34" s="10">
+        <f>SUM(L35:L35)</f>
+        <v/>
+      </c>
+      <c r="M34" s="10">
+        <f>SUM(M35:M35)</f>
+        <v/>
+      </c>
+      <c r="N34" s="10">
+        <f>SUM(N35:N35)</f>
+        <v/>
+      </c>
+      <c r="O34" s="10">
+        <f>SUM(O35:O35)</f>
+        <v/>
+      </c>
+      <c r="P34" s="10">
+        <f>SUM(D34:O34)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="34" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A34" t="inlineStr">
+    <row r="35" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t xml:space="preserve">      SHAREDSERVICESSL</t>
         </is>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="E34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="F34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="G34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="H34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="I34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="J34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="K34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="L34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="M34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="N34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="O34" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A34))</f>
-        <v/>
-      </c>
-      <c r="P34" s="4">
-        <f>SUM(D34:O34)</f>
-        <v/>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="E35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="F35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="G35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="H35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="I35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="K35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="L35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="M35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="N35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="O35" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"shared_services",'g-expenses-inc'!$E:$E,TRIM($A35))</f>
+        <v/>
+      </c>
+      <c r="P35" s="4">
+        <f>SUM(D35:O35)</f>
+        <v/>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="35" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Administration</t>
         </is>
       </c>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10">
-        <f>SUM(D36:D41)</f>
-        <v/>
-      </c>
-      <c r="E35" s="10">
-        <f>SUM(E36:E41)</f>
-        <v/>
-      </c>
-      <c r="F35" s="10">
-        <f>SUM(F36:F41)</f>
-        <v/>
-      </c>
-      <c r="G35" s="10">
-        <f>SUM(G36:G41)</f>
-        <v/>
-      </c>
-      <c r="H35" s="10">
-        <f>SUM(H36:H41)</f>
-        <v/>
-      </c>
-      <c r="I35" s="10">
-        <f>SUM(I36:I41)</f>
-        <v/>
-      </c>
-      <c r="J35" s="10">
-        <f>SUM(J36:J41)</f>
-        <v/>
-      </c>
-      <c r="K35" s="10">
-        <f>SUM(K36:K41)</f>
-        <v/>
-      </c>
-      <c r="L35" s="10">
-        <f>SUM(L36:L41)</f>
-        <v/>
-      </c>
-      <c r="M35" s="10">
-        <f>SUM(M36:M41)</f>
-        <v/>
-      </c>
-      <c r="N35" s="10">
-        <f>SUM(N36:N41)</f>
-        <v/>
-      </c>
-      <c r="O35" s="10">
-        <f>SUM(O36:O41)</f>
-        <v/>
-      </c>
-      <c r="P35" s="10">
-        <f>SUM(D35:O35)</f>
-        <v/>
-      </c>
-      <c r="Q35" s="10" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      CONTINUUM</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="E36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="F36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="G36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="H36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="I36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="J36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="K36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="L36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="M36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="N36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="O36" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A36))</f>
-        <v/>
-      </c>
-      <c r="P36" s="4">
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10">
+        <f>SUM(D37:D42)</f>
+        <v/>
+      </c>
+      <c r="E36" s="10">
+        <f>SUM(E37:E42)</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>SUM(F37:F42)</f>
+        <v/>
+      </c>
+      <c r="G36" s="10">
+        <f>SUM(G37:G42)</f>
+        <v/>
+      </c>
+      <c r="H36" s="10">
+        <f>SUM(H37:H42)</f>
+        <v/>
+      </c>
+      <c r="I36" s="10">
+        <f>SUM(I37:I42)</f>
+        <v/>
+      </c>
+      <c r="J36" s="10">
+        <f>SUM(J37:J42)</f>
+        <v/>
+      </c>
+      <c r="K36" s="10">
+        <f>SUM(K37:K42)</f>
+        <v/>
+      </c>
+      <c r="L36" s="10">
+        <f>SUM(L37:L42)</f>
+        <v/>
+      </c>
+      <c r="M36" s="10">
+        <f>SUM(M37:M42)</f>
+        <v/>
+      </c>
+      <c r="N36" s="10">
+        <f>SUM(N37:N42)</f>
+        <v/>
+      </c>
+      <c r="O36" s="10">
+        <f>SUM(O37:O42)</f>
+        <v/>
+      </c>
+      <c r="P36" s="10">
         <f>SUM(D36:O36)</f>
         <v/>
       </c>
-      <c r="Q36" s="4" t="inlineStr">
+      <c r="Q36" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -2609,7 +2612,7 @@
     <row r="37" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">      DELAWARE</t>
+          <t xml:space="preserve">      CONTINUUM</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
@@ -2666,12 +2669,16 @@
         <f>SUM(D37:O37)</f>
         <v/>
       </c>
-      <c r="Q37" s="4" t="n"/>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
     </row>
     <row r="38" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">      HUSHED</t>
+          <t xml:space="preserve">      DELAWARE</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -2733,7 +2740,7 @@
     <row r="39" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">      IPOSTAL</t>
+          <t xml:space="preserve">      HUSHED</t>
         </is>
       </c>
       <c r="B39" s="4" t="n"/>
@@ -2795,7 +2802,7 @@
     <row r="40" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">      QUICKBOOKS</t>
+          <t xml:space="preserve">      IPOSTAL</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -2857,7 +2864,7 @@
     <row r="41" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">      REGUS</t>
+          <t xml:space="preserve">      QUICKBOOKS</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -2916,199 +2923,195 @@
       </c>
       <c r="Q41" s="4" t="n"/>
     </row>
-    <row r="42" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
+    <row r="42" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      REGUS</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n"/>
+      <c r="C42" s="4" t="n"/>
+      <c r="D42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="F42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="G42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="H42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="I42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="J42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="K42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="L42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="M42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="N42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="O42" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"administration",'g-expenses-inc'!$E:$E,TRIM($A42))</f>
+        <v/>
+      </c>
+      <c r="P42" s="4">
+        <f>SUM(D42:O42)</f>
+        <v/>
+      </c>
+      <c r="Q42" s="4" t="n"/>
+    </row>
+    <row r="43" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">    Technology</t>
         </is>
       </c>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10">
-        <f>SUM(D43:D43)</f>
-        <v/>
-      </c>
-      <c r="E42" s="10">
-        <f>SUM(E43:E43)</f>
-        <v/>
-      </c>
-      <c r="F42" s="10">
-        <f>SUM(F43:F43)</f>
-        <v/>
-      </c>
-      <c r="G42" s="10">
-        <f>SUM(G43:G43)</f>
-        <v/>
-      </c>
-      <c r="H42" s="10">
-        <f>SUM(H43:H43)</f>
-        <v/>
-      </c>
-      <c r="I42" s="10">
-        <f>SUM(I43:I43)</f>
-        <v/>
-      </c>
-      <c r="J42" s="10">
-        <f>SUM(J43:J43)</f>
-        <v/>
-      </c>
-      <c r="K42" s="10">
-        <f>SUM(K43:K43)</f>
-        <v/>
-      </c>
-      <c r="L42" s="10">
-        <f>SUM(L43:L43)</f>
-        <v/>
-      </c>
-      <c r="M42" s="10">
-        <f>SUM(M43:M43)</f>
-        <v/>
-      </c>
-      <c r="N42" s="10">
-        <f>SUM(N43:N43)</f>
-        <v/>
-      </c>
-      <c r="O42" s="10">
-        <f>SUM(O43:O43)</f>
-        <v/>
-      </c>
-      <c r="P42" s="10">
-        <f>SUM(D42:O42)</f>
-        <v/>
-      </c>
-      <c r="Q42" s="10" t="inlineStr">
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10">
+        <f>SUM(D44:D44)</f>
+        <v/>
+      </c>
+      <c r="E43" s="10">
+        <f>SUM(E44:E44)</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>SUM(F44:F44)</f>
+        <v/>
+      </c>
+      <c r="G43" s="10">
+        <f>SUM(G44:G44)</f>
+        <v/>
+      </c>
+      <c r="H43" s="10">
+        <f>SUM(H44:H44)</f>
+        <v/>
+      </c>
+      <c r="I43" s="10">
+        <f>SUM(I44:I44)</f>
+        <v/>
+      </c>
+      <c r="J43" s="10">
+        <f>SUM(J44:J44)</f>
+        <v/>
+      </c>
+      <c r="K43" s="10">
+        <f>SUM(K44:K44)</f>
+        <v/>
+      </c>
+      <c r="L43" s="10">
+        <f>SUM(L44:L44)</f>
+        <v/>
+      </c>
+      <c r="M43" s="10">
+        <f>SUM(M44:M44)</f>
+        <v/>
+      </c>
+      <c r="N43" s="10">
+        <f>SUM(N44:N44)</f>
+        <v/>
+      </c>
+      <c r="O43" s="10">
+        <f>SUM(O44:O44)</f>
+        <v/>
+      </c>
+      <c r="P43" s="10">
+        <f>SUM(D43:O43)</f>
+        <v/>
+      </c>
+      <c r="Q43" s="10" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
       </c>
     </row>
-    <row r="43" hidden="1" outlineLevel="3" ht="12" customHeight="1">
-      <c r="A43" t="inlineStr">
+    <row r="44" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+      <c r="A44" t="inlineStr">
         <is>
           <t xml:space="preserve">      REVER</t>
         </is>
       </c>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="E43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="F43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="G43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="H43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="I43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="J43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="K43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="L43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="M43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="N43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="O43" s="4">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A43))</f>
-        <v/>
-      </c>
-      <c r="P43" s="4">
-        <f>SUM(D43:O43)</f>
-        <v/>
-      </c>
-      <c r="Q43" s="4" t="inlineStr">
-        <is>
-          <t>-&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" hidden="1" outlineLevel="2" ht="12" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Uncategorized Expenses</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="E44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="F44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="G44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="H44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="I44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="J44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="K44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="L44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="M44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="N44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="O44" s="10">
-        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
-        <v/>
-      </c>
-      <c r="P44" s="10">
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="E44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="F44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="G44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="H44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="I44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="J44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="K44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="L44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="M44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="N44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="O44" s="4">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"technology",'g-expenses-inc'!$E:$E,TRIM($A44))</f>
+        <v/>
+      </c>
+      <c r="P44" s="4">
         <f>SUM(D44:O44)</f>
         <v/>
       </c>
-      <c r="Q44" s="10" t="inlineStr">
+      <c r="Q44" s="4" t="inlineStr">
         <is>
           <t>-&gt;</t>
         </is>
@@ -3117,260 +3120,286 @@
     <row r="45" hidden="1" outlineLevel="2" ht="12" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Currency Adjustment</t>
+          <t xml:space="preserve">    Uncategorized Expenses</t>
         </is>
       </c>
       <c r="B45" s="10" t="n"/>
       <c r="C45" s="10" t="n"/>
-      <c r="D45" s="10" t="n"/>
-      <c r="E45" s="10" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="10" t="n"/>
-      <c r="H45" s="10" t="n"/>
-      <c r="I45" s="10" t="n"/>
-      <c r="J45" s="10" t="n"/>
-      <c r="K45" s="10" t="n"/>
-      <c r="L45" s="10" t="n"/>
-      <c r="M45" s="10" t="n"/>
-      <c r="N45" s="10" t="n"/>
-      <c r="O45" s="10" t="n"/>
+      <c r="D45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,D$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="E45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,E$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,F$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="G45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,G$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="H45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,H$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="I45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,I$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="J45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,J$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="K45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,K$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="L45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,L$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="M45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,M$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="N45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,N$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
+      <c r="O45" s="10">
+        <f>SUMIFS('g-expenses-inc'!$K:$K,'g-expenses-inc'!$A:$A,O$1,'g-expenses-inc'!$D:$D,"otros_gastos")</f>
+        <v/>
+      </c>
       <c r="P45" s="10">
         <f>SUM(D45:O45)</f>
         <v/>
       </c>
-      <c r="Q45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="12" customHeight="1">
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
-      <c r="O46" s="4" t="n"/>
-      <c r="P46" s="4">
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>-&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" hidden="1" outlineLevel="2" ht="12" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Currency Adjustment</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="10" t="n"/>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="n"/>
+      <c r="L46" s="10" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10">
         <f>SUM(D46:O46)</f>
         <v/>
       </c>
-      <c r="Q46" s="4" t="n"/>
+      <c r="Q46" s="10" t="n"/>
     </row>
     <row r="47" ht="12" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+      <c r="M47" s="4" t="n"/>
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4">
+        <f>SUM(D47:O47)</f>
+        <v/>
+      </c>
+      <c r="Q47" s="4" t="n"/>
+    </row>
+    <row r="48" ht="12" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>PROFIT</t>
         </is>
       </c>
-      <c r="B47" s="14" t="n"/>
-      <c r="C47" s="14" t="n"/>
-      <c r="D47" s="14">
-        <f>D4-D12-D32-D45</f>
-        <v/>
-      </c>
-      <c r="E47" s="14">
-        <f>E4-E12-E32-E45</f>
-        <v/>
-      </c>
-      <c r="F47" s="14">
-        <f>F4-F12-F32-F45</f>
-        <v/>
-      </c>
-      <c r="G47" s="14">
-        <f>G4-G12-G32-G45</f>
-        <v/>
-      </c>
-      <c r="H47" s="14">
-        <f>H4-H12-H32-H45</f>
-        <v/>
-      </c>
-      <c r="I47" s="14">
-        <f>I4-I12-I32-I45</f>
-        <v/>
-      </c>
-      <c r="J47" s="14">
-        <f>J4-J12-J32-J45</f>
-        <v/>
-      </c>
-      <c r="K47" s="14">
-        <f>K4-K12-K32-K45</f>
-        <v/>
-      </c>
-      <c r="L47" s="14">
-        <f>L4-L12-L32-L45</f>
-        <v/>
-      </c>
-      <c r="M47" s="14">
-        <f>M4-M12-M32-M45</f>
-        <v/>
-      </c>
-      <c r="N47" s="14">
-        <f>N4-N12-N32-N45</f>
-        <v/>
-      </c>
-      <c r="O47" s="14">
-        <f>O4-O12-O32-O45</f>
-        <v/>
-      </c>
-      <c r="P47" s="14">
-        <f>SUM(D47:O47)</f>
-        <v/>
-      </c>
-      <c r="Q47" s="14" t="n"/>
-    </row>
-    <row r="48" hidden="1" outlineLevel="1" ht="12" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16">
+        <f>D4-D13-D33-D46</f>
+        <v/>
+      </c>
+      <c r="E48" s="16">
+        <f>E4-E13-E33-E46</f>
+        <v/>
+      </c>
+      <c r="F48" s="16">
+        <f>F4-F13-F33-F46</f>
+        <v/>
+      </c>
+      <c r="G48" s="16">
+        <f>G4-G13-G33-G46</f>
+        <v/>
+      </c>
+      <c r="H48" s="16">
+        <f>H4-H13-H33-H46</f>
+        <v/>
+      </c>
+      <c r="I48" s="16">
+        <f>I4-I13-I33-I46</f>
+        <v/>
+      </c>
+      <c r="J48" s="16">
+        <f>J4-J13-J33-J46</f>
+        <v/>
+      </c>
+      <c r="K48" s="16">
+        <f>K4-K13-K33-K46</f>
+        <v/>
+      </c>
+      <c r="L48" s="16">
+        <f>L4-L13-L33-L46</f>
+        <v/>
+      </c>
+      <c r="M48" s="16">
+        <f>M4-M13-M33-M46</f>
+        <v/>
+      </c>
+      <c r="N48" s="16">
+        <f>N4-N13-N33-N46</f>
+        <v/>
+      </c>
+      <c r="O48" s="16">
+        <f>O4-O13-O33-O46</f>
+        <v/>
+      </c>
+      <c r="P48" s="16">
+        <f>SUM(D48:O48)</f>
+        <v/>
+      </c>
+      <c r="Q48" s="16" t="n"/>
+    </row>
+    <row r="49" hidden="1" outlineLevel="1" ht="12" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>% profit / product sales</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11">
-        <f>IFERROR(D47/D5,0)</f>
-        <v/>
-      </c>
-      <c r="E48" s="11">
-        <f>IFERROR(E47/E5,0)</f>
-        <v/>
-      </c>
-      <c r="F48" s="11">
-        <f>IFERROR(F47/F5,0)</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IFERROR(G47/G5,0)</f>
-        <v/>
-      </c>
-      <c r="H48" s="11">
-        <f>IFERROR(H47/H5,0)</f>
-        <v/>
-      </c>
-      <c r="I48" s="11">
-        <f>IFERROR(I47/I5,0)</f>
-        <v/>
-      </c>
-      <c r="J48" s="11">
-        <f>IFERROR(J47/J5,0)</f>
-        <v/>
-      </c>
-      <c r="K48" s="11">
-        <f>IFERROR(K47/K5,0)</f>
-        <v/>
-      </c>
-      <c r="L48" s="11">
-        <f>IFERROR(L47/L5,0)</f>
-        <v/>
-      </c>
-      <c r="M48" s="11">
-        <f>IFERROR(M47/M5,0)</f>
-        <v/>
-      </c>
-      <c r="N48" s="11">
-        <f>IFERROR(N47/N5,0)</f>
-        <v/>
-      </c>
-      <c r="O48" s="11">
-        <f>IFERROR(O47/O5,0)</f>
-        <v/>
-      </c>
-      <c r="P48" s="11">
-        <f>IFERROR(P47/P5,0)</f>
-        <v/>
-      </c>
-      <c r="Q48" s="11" t="n"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="n"/>
-      <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
-      <c r="O49" s="4" t="n"/>
-      <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n"/>
+      <c r="B49" s="13" t="n"/>
+      <c r="C49" s="13" t="n"/>
+      <c r="D49" s="13">
+        <f>IFERROR(D48/D5,0)</f>
+        <v/>
+      </c>
+      <c r="E49" s="13">
+        <f>IFERROR(E48/E5,0)</f>
+        <v/>
+      </c>
+      <c r="F49" s="13">
+        <f>IFERROR(F48/F5,0)</f>
+        <v/>
+      </c>
+      <c r="G49" s="13">
+        <f>IFERROR(G48/G5,0)</f>
+        <v/>
+      </c>
+      <c r="H49" s="13">
+        <f>IFERROR(H48/H5,0)</f>
+        <v/>
+      </c>
+      <c r="I49" s="13">
+        <f>IFERROR(I48/I5,0)</f>
+        <v/>
+      </c>
+      <c r="J49" s="13">
+        <f>IFERROR(J48/J5,0)</f>
+        <v/>
+      </c>
+      <c r="K49" s="13">
+        <f>IFERROR(K48/K5,0)</f>
+        <v/>
+      </c>
+      <c r="L49" s="13">
+        <f>IFERROR(L48/L5,0)</f>
+        <v/>
+      </c>
+      <c r="M49" s="13">
+        <f>IFERROR(M48/M5,0)</f>
+        <v/>
+      </c>
+      <c r="N49" s="13">
+        <f>IFERROR(N48/N5,0)</f>
+        <v/>
+      </c>
+      <c r="O49" s="13">
+        <f>IFERROR(O48/O5,0)</f>
+        <v/>
+      </c>
+      <c r="P49" s="13">
+        <f>IFERROR(P48/P5,0)</f>
+        <v/>
+      </c>
+      <c r="Q49" s="13" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Stock inicial marcos</t>
-        </is>
-      </c>
       <c r="B50" s="4" t="n"/>
       <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n">
-        <v>15764.34</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>13105.38</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>11635.01</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>10232.85</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>9332.9</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>8649.540000000001</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>7981.96</v>
-      </c>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
-      <c r="P50" s="4">
-        <f>SUM(D50:O50)</f>
-        <v/>
-      </c>
+      <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Stock final marcos</t>
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>Stock inicial marcos</t>
         </is>
       </c>
       <c r="B51" s="4" t="n"/>
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n">
+        <v>15764.34</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>13105.38</v>
       </c>
-      <c r="E51" s="4" t="n">
+      <c r="F51" s="4" t="n">
         <v>11635.01</v>
       </c>
-      <c r="F51" s="4" t="n">
-        <v>10217.07</v>
-      </c>
       <c r="G51" s="4" t="n">
+        <v>10232.85</v>
+      </c>
+      <c r="H51" s="4" t="n">
         <v>9332.9</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="I51" s="4" t="n">
         <v>8649.540000000001</v>
       </c>
-      <c r="I51" s="4" t="n">
-        <v>7965.46</v>
-      </c>
       <c r="J51" s="4" t="n">
-        <v>7868.12</v>
+        <v>7981.96</v>
       </c>
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
@@ -3382,6 +3411,46 @@
         <v/>
       </c>
       <c r="Q51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Stock final marcos</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n">
+        <v>13105.38</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>11635.01</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>10217.07</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>9332.9</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>8649.540000000001</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>7965.46</v>
+      </c>
+      <c r="J52" s="4" t="n">
+        <v>7547.92</v>
+      </c>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4">
+        <f>SUM(D52:O52)</f>
+        <v/>
+      </c>
+      <c r="Q52" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3391,19 +3460,19 @@
   <hyperlinks>
     <hyperlink ref="Q6" location="'i-shopify-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q7" location="'i-shopify-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q13" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q14" location="'g-expenses-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q18" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q15" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q19" location="'g-expenses-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q21" location="'g-payment-fees-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q20" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q22" location="'g-payment-fees-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q33" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q23" location="'g-payment-fees-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q34" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q35" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q36" location="'g-expenses-inc'!A1" display="-&gt;"/>
-    <hyperlink ref="Q42" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q37" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q43" location="'g-expenses-inc'!A1" display="-&gt;"/>
     <hyperlink ref="Q44" location="'g-expenses-inc'!A1" display="-&gt;"/>
+    <hyperlink ref="Q45" location="'g-expenses-inc'!A1" display="-&gt;"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3423,19 +3492,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>value</t>
         </is>
@@ -3483,7 +3552,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-11T01:04:46Z</t>
+          <t>2026-07-31T07:48:06Z</t>
         </is>
       </c>
     </row>
@@ -3517,59 +3586,59 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>line_item</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -3609,7 +3678,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H3" s="18" t="n">
+      <c r="H3" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
@@ -3655,7 +3724,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H4" s="18" t="n">
+      <c r="H4" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I4" s="4" t="n">
@@ -3701,7 +3770,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H5" s="18" t="n">
+      <c r="H5" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I5" s="4" t="n">
@@ -3747,7 +3816,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H6" s="18" t="n">
+      <c r="H6" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
@@ -3793,7 +3862,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H7" s="18" t="n">
+      <c r="H7" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I7" s="4" t="n">
@@ -3839,7 +3908,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H8" s="18" t="n">
+      <c r="H8" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I8" s="4" t="n">
@@ -3873,7 +3942,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2616.97</v>
+        <v>11552.85</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3885,11 +3954,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H9" s="18" t="n">
+      <c r="H9" s="20" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2616.97</v>
+        <v>11552.85</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -3931,79 +4000,79 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>subcategory</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="J2" s="17" t="inlineStr">
+      <c r="J2" s="19" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="K2" s="17" t="inlineStr">
+      <c r="K2" s="19" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="L2" s="17" t="inlineStr">
+      <c r="L2" s="19" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="M2" s="17" t="inlineStr">
+      <c r="M2" s="19" t="inlineStr">
         <is>
           <t>invoice_number</t>
         </is>
       </c>
-      <c r="N2" s="17" t="inlineStr">
+      <c r="N2" s="19" t="inlineStr">
         <is>
           <t>drive_url</t>
         </is>
@@ -4053,7 +4122,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J3" s="18" t="n">
+      <c r="J3" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K3" s="4" t="n">
@@ -4064,7 +4133,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="M3" s="21" t="inlineStr">
         <is>
           <t>1220</t>
         </is>
@@ -4119,7 +4188,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J4" s="18" t="n">
+      <c r="J4" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
@@ -4130,7 +4199,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M4" s="19" t="inlineStr">
+      <c r="M4" s="21" t="inlineStr">
         <is>
           <t>2172-2199</t>
         </is>
@@ -4185,7 +4254,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
+      <c r="J5" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
@@ -4196,7 +4265,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M5" s="19" t="inlineStr">
+      <c r="M5" s="21" t="inlineStr">
         <is>
           <t>34735793</t>
         </is>
@@ -4251,7 +4320,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
+      <c r="J6" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K6" s="4" t="n">
@@ -4262,7 +4331,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M6" s="19" t="inlineStr">
+      <c r="M6" s="21" t="inlineStr">
         <is>
           <t>34899776</t>
         </is>
@@ -4317,7 +4386,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
+      <c r="J7" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
@@ -4328,7 +4397,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M7" s="19" t="inlineStr">
+      <c r="M7" s="21" t="inlineStr">
         <is>
           <t>35170891</t>
         </is>
@@ -4383,7 +4452,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J8" s="18" t="n">
+      <c r="J8" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
@@ -4394,7 +4463,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M8" s="19" t="inlineStr">
+      <c r="M8" s="21" t="inlineStr">
         <is>
           <t>35204899</t>
         </is>
@@ -4449,7 +4518,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J9" s="18" t="n">
+      <c r="J9" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
@@ -4460,7 +4529,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M9" s="19" t="inlineStr">
+      <c r="M9" s="21" t="inlineStr">
         <is>
           <t>AS-93451</t>
         </is>
@@ -4515,7 +4584,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J10" s="18" t="n">
+      <c r="J10" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="4" t="n">
@@ -4526,7 +4595,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M10" s="19" t="inlineStr">
+      <c r="M10" s="21" t="inlineStr">
         <is>
           <t>AS-94908</t>
         </is>
@@ -4581,7 +4650,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n">
+      <c r="J11" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="4" t="n">
@@ -4592,7 +4661,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M11" s="19" t="inlineStr">
+      <c r="M11" s="21" t="inlineStr">
         <is>
           <t>AS-94969</t>
         </is>
@@ -4647,7 +4716,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J12" s="18" t="n">
+      <c r="J12" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
@@ -4658,7 +4727,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M12" s="19" t="inlineStr">
+      <c r="M12" s="21" t="inlineStr">
         <is>
           <t>AS-95058</t>
         </is>
@@ -4713,7 +4782,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J13" s="18" t="n">
+      <c r="J13" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="4" t="n">
@@ -4724,7 +4793,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M13" s="19" t="inlineStr">
+      <c r="M13" s="21" t="inlineStr">
         <is>
           <t>AS-95513</t>
         </is>
@@ -4779,7 +4848,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J14" s="18" t="n">
+      <c r="J14" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="4" t="n">
@@ -4790,7 +4859,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M14" s="19" t="inlineStr">
+      <c r="M14" s="21" t="inlineStr">
         <is>
           <t>AS-96265</t>
         </is>
@@ -4845,7 +4914,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J15" s="18" t="n">
+      <c r="J15" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="4" t="n">
@@ -4856,7 +4925,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M15" s="19" t="inlineStr">
+      <c r="M15" s="21" t="inlineStr">
         <is>
           <t>AS-96361</t>
         </is>
@@ -4911,7 +4980,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J16" s="18" t="n">
+      <c r="J16" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="4" t="n">
@@ -4922,7 +4991,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M16" s="19" t="inlineStr">
+      <c r="M16" s="21" t="inlineStr">
         <is>
           <t>10001458238017</t>
         </is>
@@ -4977,7 +5046,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J17" s="18" t="n">
+      <c r="J17" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="4" t="n">
@@ -4988,7 +5057,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M17" s="19" t="inlineStr">
+      <c r="M17" s="21" t="inlineStr">
         <is>
           <t>3313-43306</t>
         </is>
@@ -5043,7 +5112,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J18" s="18" t="n">
+      <c r="J18" s="20" t="n">
         <v>1.1919</v>
       </c>
       <c r="K18" s="4" t="n">
@@ -5054,7 +5123,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M18" s="19" t="inlineStr">
+      <c r="M18" s="21" t="inlineStr">
         <is>
           <t>2026-0009</t>
         </is>
@@ -5109,7 +5178,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J19" s="18" t="n">
+      <c r="J19" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="4" t="n">
@@ -5120,7 +5189,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M19" s="19" t="inlineStr">
+      <c r="M19" s="21" t="inlineStr">
         <is>
           <t>171197</t>
         </is>
@@ -5175,7 +5244,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J20" s="18" t="n">
+      <c r="J20" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="4" t="n">
@@ -5186,7 +5255,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M20" s="19" t="inlineStr">
+      <c r="M20" s="21" t="inlineStr">
         <is>
           <t>171198</t>
         </is>
@@ -5241,7 +5310,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J21" s="18" t="n">
+      <c r="J21" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="4" t="n">
@@ -5252,7 +5321,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M21" s="19" t="inlineStr">
+      <c r="M21" s="21" t="inlineStr">
         <is>
           <t>1236</t>
         </is>
@@ -5307,7 +5376,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J22" s="18" t="n">
+      <c r="J22" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="4" t="n">
@@ -5318,7 +5387,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M22" s="19" t="inlineStr">
+      <c r="M22" s="21" t="inlineStr">
         <is>
           <t>2353-3823</t>
         </is>
@@ -5373,7 +5442,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J23" s="18" t="n">
+      <c r="J23" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="4" t="n">
@@ -5384,7 +5453,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M23" s="19" t="inlineStr">
+      <c r="M23" s="21" t="inlineStr">
         <is>
           <t>35389577</t>
         </is>
@@ -5439,7 +5508,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J24" s="18" t="n">
+      <c r="J24" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="4" t="n">
@@ -5450,7 +5519,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M24" s="19" t="inlineStr">
+      <c r="M24" s="21" t="inlineStr">
         <is>
           <t>35565709</t>
         </is>
@@ -5505,7 +5574,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J25" s="18" t="n">
+      <c r="J25" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="4" t="n">
@@ -5516,7 +5585,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M25" s="19" t="inlineStr">
+      <c r="M25" s="21" t="inlineStr">
         <is>
           <t>35722393</t>
         </is>
@@ -5571,7 +5640,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J26" s="18" t="n">
+      <c r="J26" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="4" t="n">
@@ -5582,7 +5651,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M26" s="19" t="inlineStr">
+      <c r="M26" s="21" t="inlineStr">
         <is>
           <t>AS-97102</t>
         </is>
@@ -5637,7 +5706,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J27" s="18" t="n">
+      <c r="J27" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K27" s="4" t="n">
@@ -5648,7 +5717,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M27" s="19" t="inlineStr">
+      <c r="M27" s="21" t="inlineStr">
         <is>
           <t>AS-97313</t>
         </is>
@@ -5703,7 +5772,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J28" s="18" t="n">
+      <c r="J28" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K28" s="4" t="n">
@@ -5714,7 +5783,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M28" s="19" t="inlineStr">
+      <c r="M28" s="21" t="inlineStr">
         <is>
           <t>AS-97766</t>
         </is>
@@ -5769,7 +5838,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J29" s="18" t="n">
+      <c r="J29" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K29" s="4" t="n">
@@ -5780,7 +5849,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M29" s="19" t="inlineStr">
+      <c r="M29" s="21" t="inlineStr">
         <is>
           <t>AS-97929</t>
         </is>
@@ -5835,7 +5904,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J30" s="18" t="n">
+      <c r="J30" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K30" s="4" t="n">
@@ -5846,7 +5915,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M30" s="19" t="inlineStr">
+      <c r="M30" s="21" t="inlineStr">
         <is>
           <t>AS-98182</t>
         </is>
@@ -5901,7 +5970,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J31" s="18" t="n">
+      <c r="J31" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K31" s="4" t="n">
@@ -5912,7 +5981,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M31" s="19" t="inlineStr">
+      <c r="M31" s="21" t="inlineStr">
         <is>
           <t>AS-98184</t>
         </is>
@@ -5967,7 +6036,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J32" s="18" t="n">
+      <c r="J32" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K32" s="4" t="n">
@@ -5978,7 +6047,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M32" s="19" t="inlineStr">
+      <c r="M32" s="21" t="inlineStr">
         <is>
           <t>AS-98186</t>
         </is>
@@ -6033,7 +6102,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J33" s="18" t="n">
+      <c r="J33" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K33" s="4" t="n">
@@ -6044,7 +6113,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M33" s="19" t="inlineStr">
+      <c r="M33" s="21" t="inlineStr">
         <is>
           <t>AS-98295</t>
         </is>
@@ -6099,7 +6168,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J34" s="18" t="n">
+      <c r="J34" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K34" s="4" t="n">
@@ -6110,7 +6179,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M34" s="19" t="inlineStr">
+      <c r="M34" s="21" t="inlineStr">
         <is>
           <t>AS-98569</t>
         </is>
@@ -6165,7 +6234,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J35" s="18" t="n">
+      <c r="J35" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K35" s="4" t="n">
@@ -6176,7 +6245,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M35" s="19" t="inlineStr">
+      <c r="M35" s="21" t="inlineStr">
         <is>
           <t>AS-98850</t>
         </is>
@@ -6231,7 +6300,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J36" s="18" t="n">
+      <c r="J36" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K36" s="4" t="n">
@@ -6242,7 +6311,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M36" s="19" t="inlineStr">
+      <c r="M36" s="21" t="inlineStr">
         <is>
           <t>AS-99137</t>
         </is>
@@ -6297,7 +6366,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J37" s="18" t="n">
+      <c r="J37" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K37" s="4" t="n">
@@ -6308,7 +6377,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M37" s="19" t="inlineStr">
+      <c r="M37" s="21" t="inlineStr">
         <is>
           <t>AS-99148</t>
         </is>
@@ -6363,7 +6432,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J38" s="18" t="n">
+      <c r="J38" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K38" s="4" t="n">
@@ -6374,7 +6443,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M38" s="19" t="inlineStr">
+      <c r="M38" s="21" t="inlineStr">
         <is>
           <t>AS-99337</t>
         </is>
@@ -6429,7 +6498,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J39" s="18" t="n">
+      <c r="J39" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K39" s="4" t="n">
@@ -6440,7 +6509,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M39" s="19" t="inlineStr">
+      <c r="M39" s="21" t="inlineStr">
         <is>
           <t>AS-99436</t>
         </is>
@@ -6495,7 +6564,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J40" s="18" t="n">
+      <c r="J40" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K40" s="4" t="n">
@@ -6506,7 +6575,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M40" s="19" t="inlineStr">
+      <c r="M40" s="21" t="inlineStr">
         <is>
           <t>AS-99460</t>
         </is>
@@ -6561,7 +6630,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J41" s="18" t="n">
+      <c r="J41" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K41" s="4" t="n">
@@ -6572,7 +6641,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M41" s="19" t="inlineStr">
+      <c r="M41" s="21" t="inlineStr">
         <is>
           <t>AS-99461</t>
         </is>
@@ -6627,7 +6696,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J42" s="18" t="n">
+      <c r="J42" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K42" s="4" t="n">
@@ -6638,7 +6707,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M42" s="19" t="inlineStr">
+      <c r="M42" s="21" t="inlineStr">
         <is>
           <t>AS-99636</t>
         </is>
@@ -6693,7 +6762,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J43" s="18" t="n">
+      <c r="J43" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K43" s="4" t="n">
@@ -6704,7 +6773,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M43" s="19" t="inlineStr">
+      <c r="M43" s="21" t="inlineStr">
         <is>
           <t>AS-99795</t>
         </is>
@@ -6759,7 +6828,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J44" s="18" t="n">
+      <c r="J44" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="4" t="n">
@@ -6770,7 +6839,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M44" s="19" t="inlineStr">
+      <c r="M44" s="21" t="inlineStr">
         <is>
           <t>10001466838914</t>
         </is>
@@ -6825,7 +6894,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J45" s="18" t="n">
+      <c r="J45" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K45" s="4" t="n">
@@ -6836,7 +6905,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M45" s="19" t="inlineStr">
+      <c r="M45" s="21" t="inlineStr">
         <is>
           <t>3313-43718</t>
         </is>
@@ -6891,7 +6960,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J46" s="18" t="n">
+      <c r="J46" s="20" t="n">
         <v>1.1805</v>
       </c>
       <c r="K46" s="4" t="n">
@@ -6902,7 +6971,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M46" s="19" t="inlineStr">
+      <c r="M46" s="21" t="inlineStr">
         <is>
           <t>2026-0014</t>
         </is>
@@ -6957,7 +7026,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J47" s="18" t="n">
+      <c r="J47" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K47" s="4" t="n">
@@ -6968,7 +7037,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M47" s="19" t="inlineStr">
+      <c r="M47" s="21" t="inlineStr">
         <is>
           <t>171420</t>
         </is>
@@ -7023,7 +7092,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J48" s="18" t="n">
+      <c r="J48" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K48" s="4" t="n">
@@ -7034,7 +7103,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M48" s="19" t="inlineStr">
+      <c r="M48" s="21" t="inlineStr">
         <is>
           <t>171421</t>
         </is>
@@ -7089,7 +7158,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J49" s="18" t="n">
+      <c r="J49" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K49" s="4" t="n">
@@ -7100,7 +7169,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M49" s="19" t="inlineStr">
+      <c r="M49" s="21" t="inlineStr">
         <is>
           <t>1253</t>
         </is>
@@ -7155,7 +7224,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J50" s="18" t="n">
+      <c r="J50" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K50" s="4" t="n">
@@ -7166,7 +7235,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M50" s="19" t="inlineStr">
+      <c r="M50" s="21" t="inlineStr">
         <is>
           <t>29482W6G</t>
         </is>
@@ -7221,7 +7290,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J51" s="18" t="n">
+      <c r="J51" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K51" s="4" t="n">
@@ -7232,7 +7301,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M51" s="19" t="inlineStr">
+      <c r="M51" s="21" t="inlineStr">
         <is>
           <t>6FF58AC</t>
         </is>
@@ -7287,7 +7356,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J52" s="18" t="n">
+      <c r="J52" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K52" s="4" t="n">
@@ -7298,7 +7367,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M52" s="19" t="inlineStr">
+      <c r="M52" s="21" t="inlineStr">
         <is>
           <t>2262-7837</t>
         </is>
@@ -7353,7 +7422,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J53" s="18" t="n">
+      <c r="J53" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K53" s="4" t="n">
@@ -7364,7 +7433,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M53" s="19" t="inlineStr">
+      <c r="M53" s="21" t="inlineStr">
         <is>
           <t>35894810</t>
         </is>
@@ -7419,7 +7488,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J54" s="18" t="n">
+      <c r="J54" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K54" s="4" t="n">
@@ -7430,7 +7499,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M54" s="19" t="inlineStr">
+      <c r="M54" s="21" t="inlineStr">
         <is>
           <t>35920058</t>
         </is>
@@ -7485,7 +7554,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J55" s="18" t="n">
+      <c r="J55" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K55" s="4" t="n">
@@ -7496,7 +7565,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M55" s="19" t="inlineStr">
+      <c r="M55" s="21" t="inlineStr">
         <is>
           <t>36093781</t>
         </is>
@@ -7551,7 +7620,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J56" s="18" t="n">
+      <c r="J56" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K56" s="4" t="n">
@@ -7562,7 +7631,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M56" s="19" t="inlineStr">
+      <c r="M56" s="21" t="inlineStr">
         <is>
           <t>36265975</t>
         </is>
@@ -7617,7 +7686,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J57" s="18" t="n">
+      <c r="J57" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K57" s="4" t="n">
@@ -7628,7 +7697,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M57" s="19" t="inlineStr">
+      <c r="M57" s="21" t="inlineStr">
         <is>
           <t>36427002</t>
         </is>
@@ -7683,7 +7752,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J58" s="18" t="n">
+      <c r="J58" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K58" s="4" t="n">
@@ -7694,7 +7763,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M58" s="19" t="inlineStr">
+      <c r="M58" s="21" t="inlineStr">
         <is>
           <t>36541238</t>
         </is>
@@ -7749,7 +7818,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J59" s="18" t="n">
+      <c r="J59" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K59" s="4" t="n">
@@ -7760,7 +7829,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M59" s="19" t="inlineStr">
+      <c r="M59" s="21" t="inlineStr">
         <is>
           <t>36584953</t>
         </is>
@@ -7815,7 +7884,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J60" s="18" t="n">
+      <c r="J60" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K60" s="4" t="n">
@@ -7826,7 +7895,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M60" s="19" t="inlineStr">
+      <c r="M60" s="21" t="inlineStr">
         <is>
           <t>36600953</t>
         </is>
@@ -7881,7 +7950,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J61" s="18" t="n">
+      <c r="J61" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K61" s="4" t="n">
@@ -7892,7 +7961,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M61" s="19" t="inlineStr">
+      <c r="M61" s="21" t="inlineStr">
         <is>
           <t>AS-100001</t>
         </is>
@@ -7947,7 +8016,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J62" s="18" t="n">
+      <c r="J62" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K62" s="4" t="n">
@@ -7958,7 +8027,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M62" s="19" t="inlineStr">
+      <c r="M62" s="21" t="inlineStr">
         <is>
           <t>AS-100189</t>
         </is>
@@ -8013,7 +8082,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J63" s="18" t="n">
+      <c r="J63" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K63" s="4" t="n">
@@ -8024,7 +8093,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M63" s="19" t="inlineStr">
+      <c r="M63" s="21" t="inlineStr">
         <is>
           <t>AS-100208</t>
         </is>
@@ -8079,7 +8148,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J64" s="18" t="n">
+      <c r="J64" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K64" s="4" t="n">
@@ -8090,7 +8159,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M64" s="19" t="inlineStr">
+      <c r="M64" s="21" t="inlineStr">
         <is>
           <t>AS-100505</t>
         </is>
@@ -8145,7 +8214,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J65" s="18" t="n">
+      <c r="J65" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K65" s="4" t="n">
@@ -8156,7 +8225,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M65" s="19" t="inlineStr">
+      <c r="M65" s="21" t="inlineStr">
         <is>
           <t>AS-100874</t>
         </is>
@@ -8211,7 +8280,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J66" s="18" t="n">
+      <c r="J66" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K66" s="4" t="n">
@@ -8222,7 +8291,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M66" s="19" t="inlineStr">
+      <c r="M66" s="21" t="inlineStr">
         <is>
           <t>AS-100996</t>
         </is>
@@ -8277,7 +8346,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J67" s="18" t="n">
+      <c r="J67" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K67" s="4" t="n">
@@ -8288,7 +8357,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M67" s="19" t="inlineStr">
+      <c r="M67" s="21" t="inlineStr">
         <is>
           <t>AS-101113</t>
         </is>
@@ -8343,7 +8412,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J68" s="18" t="n">
+      <c r="J68" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K68" s="4" t="n">
@@ -8354,7 +8423,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M68" s="19" t="inlineStr">
+      <c r="M68" s="21" t="inlineStr">
         <is>
           <t>AS-101200</t>
         </is>
@@ -8409,7 +8478,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J69" s="18" t="n">
+      <c r="J69" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K69" s="4" t="n">
@@ -8420,7 +8489,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M69" s="19" t="inlineStr">
+      <c r="M69" s="21" t="inlineStr">
         <is>
           <t>AS-101203</t>
         </is>
@@ -8475,7 +8544,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J70" s="18" t="n">
+      <c r="J70" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K70" s="4" t="n">
@@ -8486,7 +8555,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M70" s="19" t="inlineStr">
+      <c r="M70" s="21" t="inlineStr">
         <is>
           <t>AS-101378</t>
         </is>
@@ -8541,7 +8610,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J71" s="18" t="n">
+      <c r="J71" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K71" s="4" t="n">
@@ -8552,7 +8621,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M71" s="19" t="inlineStr">
+      <c r="M71" s="21" t="inlineStr">
         <is>
           <t>AS-101565</t>
         </is>
@@ -8607,7 +8676,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J72" s="18" t="n">
+      <c r="J72" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K72" s="4" t="n">
@@ -8618,7 +8687,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M72" s="19" t="inlineStr">
+      <c r="M72" s="21" t="inlineStr">
         <is>
           <t>AS-101625</t>
         </is>
@@ -8673,7 +8742,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J73" s="18" t="n">
+      <c r="J73" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K73" s="4" t="n">
@@ -8684,7 +8753,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M73" s="19" t="inlineStr">
+      <c r="M73" s="21" t="inlineStr">
         <is>
           <t>AS-101687</t>
         </is>
@@ -8739,7 +8808,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J74" s="18" t="n">
+      <c r="J74" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K74" s="4" t="n">
@@ -8750,7 +8819,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M74" s="19" t="inlineStr">
+      <c r="M74" s="21" t="inlineStr">
         <is>
           <t>AS-101720</t>
         </is>
@@ -8805,7 +8874,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J75" s="18" t="n">
+      <c r="J75" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K75" s="4" t="n">
@@ -8816,7 +8885,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M75" s="19" t="inlineStr">
+      <c r="M75" s="21" t="inlineStr">
         <is>
           <t>AS-101875</t>
         </is>
@@ -8871,7 +8940,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J76" s="18" t="n">
+      <c r="J76" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K76" s="4" t="n">
@@ -8882,7 +8951,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M76" s="19" t="inlineStr">
+      <c r="M76" s="21" t="inlineStr">
         <is>
           <t>AS-101899</t>
         </is>
@@ -8937,7 +9006,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J77" s="18" t="n">
+      <c r="J77" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K77" s="4" t="n">
@@ -8948,7 +9017,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M77" s="19" t="inlineStr">
+      <c r="M77" s="21" t="inlineStr">
         <is>
           <t>AS-101925</t>
         </is>
@@ -9003,7 +9072,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J78" s="18" t="n">
+      <c r="J78" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="4" t="n">
@@ -9014,7 +9083,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M78" s="19" t="inlineStr">
+      <c r="M78" s="21" t="inlineStr">
         <is>
           <t>AS-101927</t>
         </is>
@@ -9069,7 +9138,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J79" s="18" t="n">
+      <c r="J79" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K79" s="4" t="n">
@@ -9080,7 +9149,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M79" s="19" t="inlineStr">
+      <c r="M79" s="21" t="inlineStr">
         <is>
           <t>AS-101932</t>
         </is>
@@ -9135,7 +9204,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J80" s="18" t="n">
+      <c r="J80" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K80" s="4" t="n">
@@ -9146,7 +9215,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M80" s="19" t="inlineStr">
+      <c r="M80" s="21" t="inlineStr">
         <is>
           <t>AS-102156</t>
         </is>
@@ -9201,7 +9270,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J81" s="18" t="n">
+      <c r="J81" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K81" s="4" t="n">
@@ -9212,7 +9281,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M81" s="19" t="inlineStr">
+      <c r="M81" s="21" t="inlineStr">
         <is>
           <t>AS-102233</t>
         </is>
@@ -9267,7 +9336,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J82" s="18" t="n">
+      <c r="J82" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K82" s="4" t="n">
@@ -9278,7 +9347,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M82" s="19" t="inlineStr">
+      <c r="M82" s="21" t="inlineStr">
         <is>
           <t>AS-102527</t>
         </is>
@@ -9333,7 +9402,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J83" s="18" t="n">
+      <c r="J83" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K83" s="4" t="n">
@@ -9344,7 +9413,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M83" s="19" t="inlineStr">
+      <c r="M83" s="21" t="inlineStr">
         <is>
           <t>AS-102584</t>
         </is>
@@ -9399,7 +9468,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J84" s="18" t="n">
+      <c r="J84" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K84" s="4" t="n">
@@ -9410,7 +9479,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M84" s="19" t="inlineStr">
+      <c r="M84" s="21" t="inlineStr">
         <is>
           <t>AS-102713</t>
         </is>
@@ -9465,7 +9534,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J85" s="18" t="n">
+      <c r="J85" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K85" s="4" t="n">
@@ -9476,7 +9545,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M85" s="19" t="inlineStr">
+      <c r="M85" s="21" t="inlineStr">
         <is>
           <t>AS-102769</t>
         </is>
@@ -9531,7 +9600,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J86" s="18" t="n">
+      <c r="J86" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K86" s="4" t="n">
@@ -9542,7 +9611,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M86" s="19" t="inlineStr">
+      <c r="M86" s="21" t="inlineStr">
         <is>
           <t>AS-102793</t>
         </is>
@@ -9597,7 +9666,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J87" s="18" t="n">
+      <c r="J87" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K87" s="4" t="n">
@@ -9608,7 +9677,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M87" s="19" t="inlineStr">
+      <c r="M87" s="21" t="inlineStr">
         <is>
           <t>AS-102814</t>
         </is>
@@ -9663,7 +9732,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J88" s="18" t="n">
+      <c r="J88" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K88" s="4" t="n">
@@ -9674,7 +9743,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M88" s="19" t="inlineStr">
+      <c r="M88" s="21" t="inlineStr">
         <is>
           <t>AS-99872</t>
         </is>
@@ -9729,7 +9798,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J89" s="18" t="n">
+      <c r="J89" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K89" s="4" t="n">
@@ -9740,7 +9809,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M89" s="19" t="inlineStr">
+      <c r="M89" s="21" t="inlineStr">
         <is>
           <t>10001475281494</t>
         </is>
@@ -9795,7 +9864,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J90" s="18" t="n">
+      <c r="J90" s="20" t="n">
         <v>1.1498</v>
       </c>
       <c r="K90" s="4" t="n">
@@ -9806,7 +9875,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M90" s="19" t="inlineStr">
+      <c r="M90" s="21" t="inlineStr">
         <is>
           <t>2026-0017</t>
         </is>
@@ -9861,7 +9930,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J91" s="18" t="n">
+      <c r="J91" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K91" s="4" t="n">
@@ -9872,7 +9941,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M91" s="19" t="inlineStr">
+      <c r="M91" s="21" t="inlineStr">
         <is>
           <t>171663</t>
         </is>
@@ -9927,7 +9996,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J92" s="18" t="n">
+      <c r="J92" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K92" s="4" t="n">
@@ -9938,7 +10007,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M92" s="19" t="inlineStr">
+      <c r="M92" s="21" t="inlineStr">
         <is>
           <t>171664</t>
         </is>
@@ -9993,7 +10062,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J93" s="18" t="n">
+      <c r="J93" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K93" s="4" t="n">
@@ -10004,7 +10073,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M93" s="19" t="inlineStr">
+      <c r="M93" s="21" t="inlineStr">
         <is>
           <t>1268</t>
         </is>
@@ -10059,7 +10128,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J94" s="18" t="n">
+      <c r="J94" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K94" s="4" t="n">
@@ -10070,7 +10139,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M94" s="19" t="inlineStr">
+      <c r="M94" s="21" t="inlineStr">
         <is>
           <t>DZWHFH4</t>
         </is>
@@ -10125,7 +10194,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J95" s="18" t="n">
+      <c r="J95" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K95" s="4" t="n">
@@ -10136,7 +10205,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M95" s="19" t="inlineStr">
+      <c r="M95" s="21" t="inlineStr">
         <is>
           <t>36752641</t>
         </is>
@@ -10191,7 +10260,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J96" s="18" t="n">
+      <c r="J96" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K96" s="4" t="n">
@@ -10202,7 +10271,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M96" s="19" t="inlineStr">
+      <c r="M96" s="21" t="inlineStr">
         <is>
           <t>36951380</t>
         </is>
@@ -10257,7 +10326,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J97" s="18" t="n">
+      <c r="J97" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K97" s="4" t="n">
@@ -10268,7 +10337,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M97" s="19" t="inlineStr">
+      <c r="M97" s="21" t="inlineStr">
         <is>
           <t>37116827</t>
         </is>
@@ -10323,7 +10392,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J98" s="18" t="n">
+      <c r="J98" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K98" s="4" t="n">
@@ -10334,7 +10403,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M98" s="19" t="inlineStr">
+      <c r="M98" s="21" t="inlineStr">
         <is>
           <t>37277911</t>
         </is>
@@ -10389,7 +10458,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J99" s="18" t="n">
+      <c r="J99" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K99" s="4" t="n">
@@ -10400,7 +10469,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M99" s="19" t="inlineStr">
+      <c r="M99" s="21" t="inlineStr">
         <is>
           <t>37337792</t>
         </is>
@@ -10455,7 +10524,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J100" s="18" t="n">
+      <c r="J100" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K100" s="4" t="n">
@@ -10466,7 +10535,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M100" s="19" t="inlineStr">
+      <c r="M100" s="21" t="inlineStr">
         <is>
           <t>4403771-AS-102981</t>
         </is>
@@ -10521,7 +10590,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J101" s="18" t="n">
+      <c r="J101" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K101" s="4" t="n">
@@ -10532,7 +10601,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M101" s="19" t="inlineStr">
+      <c r="M101" s="21" t="inlineStr">
         <is>
           <t>4403772-AS-102832</t>
         </is>
@@ -10587,7 +10656,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J102" s="18" t="n">
+      <c r="J102" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K102" s="4" t="n">
@@ -10598,7 +10667,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M102" s="19" t="inlineStr">
+      <c r="M102" s="21" t="inlineStr">
         <is>
           <t>4409934-AS-103327</t>
         </is>
@@ -10653,7 +10722,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J103" s="18" t="n">
+      <c r="J103" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K103" s="4" t="n">
@@ -10664,7 +10733,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M103" s="19" t="inlineStr">
+      <c r="M103" s="21" t="inlineStr">
         <is>
           <t>4409935-AS-103109</t>
         </is>
@@ -10719,7 +10788,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J104" s="18" t="n">
+      <c r="J104" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K104" s="4" t="n">
@@ -10730,7 +10799,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M104" s="19" t="inlineStr">
+      <c r="M104" s="21" t="inlineStr">
         <is>
           <t>4411288-AS-103259</t>
         </is>
@@ -10785,7 +10854,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J105" s="18" t="n">
+      <c r="J105" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K105" s="4" t="n">
@@ -10796,7 +10865,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M105" s="19" t="inlineStr">
+      <c r="M105" s="21" t="inlineStr">
         <is>
           <t>4412390-AS-103601</t>
         </is>
@@ -10851,7 +10920,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J106" s="18" t="n">
+      <c r="J106" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K106" s="4" t="n">
@@ -10862,7 +10931,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M106" s="19" t="inlineStr">
+      <c r="M106" s="21" t="inlineStr">
         <is>
           <t>4413197-AS-103687</t>
         </is>
@@ -10917,7 +10986,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J107" s="18" t="n">
+      <c r="J107" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K107" s="4" t="n">
@@ -10928,7 +10997,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M107" s="19" t="inlineStr">
+      <c r="M107" s="21" t="inlineStr">
         <is>
           <t>4413198-AS-103519</t>
         </is>
@@ -10983,7 +11052,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J108" s="18" t="n">
+      <c r="J108" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K108" s="4" t="n">
@@ -10994,7 +11063,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M108" s="19" t="inlineStr">
+      <c r="M108" s="21" t="inlineStr">
         <is>
           <t>4416660-AS-103846</t>
         </is>
@@ -11049,7 +11118,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J109" s="18" t="n">
+      <c r="J109" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K109" s="4" t="n">
@@ -11060,7 +11129,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M109" s="19" t="inlineStr">
+      <c r="M109" s="21" t="inlineStr">
         <is>
           <t>4417786-AS-104125</t>
         </is>
@@ -11115,7 +11184,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J110" s="18" t="n">
+      <c r="J110" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K110" s="4" t="n">
@@ -11126,7 +11195,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M110" s="19" t="inlineStr">
+      <c r="M110" s="21" t="inlineStr">
         <is>
           <t>4421562-AS-104370</t>
         </is>
@@ -11181,7 +11250,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J111" s="18" t="n">
+      <c r="J111" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K111" s="4" t="n">
@@ -11192,7 +11261,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M111" s="19" t="inlineStr">
+      <c r="M111" s="21" t="inlineStr">
         <is>
           <t>4425411-AS-104643</t>
         </is>
@@ -11247,7 +11316,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J112" s="18" t="n">
+      <c r="J112" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K112" s="4" t="n">
@@ -11258,7 +11327,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M112" s="19" t="inlineStr">
+      <c r="M112" s="21" t="inlineStr">
         <is>
           <t>4425412-AS-104694</t>
         </is>
@@ -11313,7 +11382,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J113" s="18" t="n">
+      <c r="J113" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K113" s="4" t="n">
@@ -11324,7 +11393,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M113" s="19" t="inlineStr">
+      <c r="M113" s="21" t="inlineStr">
         <is>
           <t>4425413-AS-104525</t>
         </is>
@@ -11379,7 +11448,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J114" s="18" t="n">
+      <c r="J114" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K114" s="4" t="n">
@@ -11390,7 +11459,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M114" s="19" t="inlineStr">
+      <c r="M114" s="21" t="inlineStr">
         <is>
           <t>4425414-AS-104577</t>
         </is>
@@ -11445,7 +11514,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J115" s="18" t="n">
+      <c r="J115" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K115" s="4" t="n">
@@ -11456,7 +11525,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M115" s="19" t="inlineStr">
+      <c r="M115" s="21" t="inlineStr">
         <is>
           <t>4426924-AS-104733</t>
         </is>
@@ -11511,7 +11580,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J116" s="18" t="n">
+      <c r="J116" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K116" s="4" t="n">
@@ -11522,7 +11591,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M116" s="19" t="inlineStr">
+      <c r="M116" s="21" t="inlineStr">
         <is>
           <t>4426925-AS-104749</t>
         </is>
@@ -11577,7 +11646,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J117" s="18" t="n">
+      <c r="J117" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K117" s="4" t="n">
@@ -11588,7 +11657,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M117" s="19" t="inlineStr">
+      <c r="M117" s="21" t="inlineStr">
         <is>
           <t>4426926-AS-104768</t>
         </is>
@@ -11643,7 +11712,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J118" s="18" t="n">
+      <c r="J118" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K118" s="4" t="n">
@@ -11654,7 +11723,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M118" s="19" t="inlineStr">
+      <c r="M118" s="21" t="inlineStr">
         <is>
           <t>4428117-AS-104525</t>
         </is>
@@ -11709,7 +11778,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J119" s="18" t="n">
+      <c r="J119" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K119" s="4" t="n">
@@ -11720,7 +11789,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M119" s="19" t="inlineStr">
+      <c r="M119" s="21" t="inlineStr">
         <is>
           <t>4428118-AS-104577</t>
         </is>
@@ -11775,7 +11844,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J120" s="18" t="n">
+      <c r="J120" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K120" s="4" t="n">
@@ -11786,7 +11855,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M120" s="19" t="inlineStr">
+      <c r="M120" s="21" t="inlineStr">
         <is>
           <t>4428119-AS-104835</t>
         </is>
@@ -11841,7 +11910,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J121" s="18" t="n">
+      <c r="J121" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K121" s="4" t="n">
@@ -11852,7 +11921,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M121" s="19" t="inlineStr">
+      <c r="M121" s="21" t="inlineStr">
         <is>
           <t>4428120-AS-104643</t>
         </is>
@@ -11907,7 +11976,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J122" s="18" t="n">
+      <c r="J122" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K122" s="4" t="n">
@@ -11918,7 +11987,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M122" s="19" t="inlineStr">
+      <c r="M122" s="21" t="inlineStr">
         <is>
           <t>4428121-AS-104694</t>
         </is>
@@ -11973,7 +12042,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J123" s="18" t="n">
+      <c r="J123" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K123" s="4" t="n">
@@ -11984,7 +12053,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M123" s="19" t="inlineStr">
+      <c r="M123" s="21" t="inlineStr">
         <is>
           <t>4428965-AS-104863</t>
         </is>
@@ -12039,7 +12108,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J124" s="18" t="n">
+      <c r="J124" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K124" s="4" t="n">
@@ -12050,7 +12119,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M124" s="19" t="inlineStr">
+      <c r="M124" s="21" t="inlineStr">
         <is>
           <t>4431846-AS-105060</t>
         </is>
@@ -12105,7 +12174,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J125" s="18" t="n">
+      <c r="J125" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K125" s="4" t="n">
@@ -12116,7 +12185,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M125" s="19" t="inlineStr">
+      <c r="M125" s="21" t="inlineStr">
         <is>
           <t>4433113-AS-105219</t>
         </is>
@@ -12171,7 +12240,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J126" s="18" t="n">
+      <c r="J126" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K126" s="4" t="n">
@@ -12182,7 +12251,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M126" s="19" t="inlineStr">
+      <c r="M126" s="21" t="inlineStr">
         <is>
           <t>4433114-AS-105230</t>
         </is>
@@ -12237,7 +12306,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J127" s="18" t="n">
+      <c r="J127" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K127" s="4" t="n">
@@ -12248,7 +12317,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M127" s="19" t="inlineStr">
+      <c r="M127" s="21" t="inlineStr">
         <is>
           <t>4434438-AS-105257</t>
         </is>
@@ -12303,7 +12372,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J128" s="18" t="n">
+      <c r="J128" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K128" s="4" t="n">
@@ -12314,7 +12383,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M128" s="19" t="inlineStr">
+      <c r="M128" s="21" t="inlineStr">
         <is>
           <t>4434439-AS-105289</t>
         </is>
@@ -12369,7 +12438,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J129" s="18" t="n">
+      <c r="J129" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K129" s="4" t="n">
@@ -12380,7 +12449,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M129" s="19" t="inlineStr">
+      <c r="M129" s="21" t="inlineStr">
         <is>
           <t>4436056-AS-105418</t>
         </is>
@@ -12435,7 +12504,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J130" s="18" t="n">
+      <c r="J130" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K130" s="4" t="n">
@@ -12446,7 +12515,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M130" s="19" t="inlineStr">
+      <c r="M130" s="21" t="inlineStr">
         <is>
           <t>10001483675456</t>
         </is>
@@ -12501,7 +12570,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J131" s="18" t="n">
+      <c r="J131" s="20" t="n">
         <v>1.1702</v>
       </c>
       <c r="K131" s="4" t="n">
@@ -12512,7 +12581,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M131" s="19" t="inlineStr">
+      <c r="M131" s="21" t="inlineStr">
         <is>
           <t>2026-0024</t>
         </is>
@@ -12567,7 +12636,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J132" s="18" t="n">
+      <c r="J132" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K132" s="4" t="n">
@@ -12578,7 +12647,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M132" s="19" t="inlineStr">
+      <c r="M132" s="21" t="inlineStr">
         <is>
           <t>171902</t>
         </is>
@@ -12633,7 +12702,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J133" s="18" t="n">
+      <c r="J133" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K133" s="4" t="n">
@@ -12644,7 +12713,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M133" s="19" t="inlineStr">
+      <c r="M133" s="21" t="inlineStr">
         <is>
           <t>171903</t>
         </is>
@@ -12699,7 +12768,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J134" s="18" t="n">
+      <c r="J134" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K134" s="4" t="n">
@@ -12710,7 +12779,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M134" s="19" t="inlineStr">
+      <c r="M134" s="21" t="inlineStr">
         <is>
           <t>1285</t>
         </is>
@@ -12765,7 +12834,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J135" s="18" t="n">
+      <c r="J135" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K135" s="4" t="n">
@@ -12776,7 +12845,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M135" s="19" t="inlineStr">
+      <c r="M135" s="21" t="inlineStr">
         <is>
           <t>2264-3993</t>
         </is>
@@ -12831,7 +12900,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J136" s="18" t="n">
+      <c r="J136" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K136" s="4" t="n">
@@ -12842,7 +12911,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M136" s="19" t="inlineStr">
+      <c r="M136" s="21" t="inlineStr">
         <is>
           <t>37443283</t>
         </is>
@@ -12897,7 +12966,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J137" s="18" t="n">
+      <c r="J137" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K137" s="4" t="n">
@@ -12908,7 +12977,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M137" s="19" t="inlineStr">
+      <c r="M137" s="21" t="inlineStr">
         <is>
           <t>37611360</t>
         </is>
@@ -12963,7 +13032,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J138" s="18" t="n">
+      <c r="J138" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K138" s="4" t="n">
@@ -12974,7 +13043,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M138" s="19" t="inlineStr">
+      <c r="M138" s="21" t="inlineStr">
         <is>
           <t>37772455</t>
         </is>
@@ -13029,7 +13098,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J139" s="18" t="n">
+      <c r="J139" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K139" s="4" t="n">
@@ -13040,7 +13109,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M139" s="19" t="inlineStr">
+      <c r="M139" s="21" t="inlineStr">
         <is>
           <t>37933367</t>
         </is>
@@ -13095,7 +13164,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J140" s="18" t="n">
+      <c r="J140" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K140" s="4" t="n">
@@ -13106,7 +13175,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M140" s="19" t="inlineStr">
+      <c r="M140" s="21" t="inlineStr">
         <is>
           <t>38027880</t>
         </is>
@@ -13161,7 +13230,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J141" s="18" t="n">
+      <c r="J141" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K141" s="4" t="n">
@@ -13172,7 +13241,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M141" s="19" t="inlineStr">
+      <c r="M141" s="21" t="inlineStr">
         <is>
           <t>38088985</t>
         </is>
@@ -13227,7 +13296,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J142" s="18" t="n">
+      <c r="J142" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K142" s="4" t="n">
@@ -13238,7 +13307,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M142" s="19" t="inlineStr">
+      <c r="M142" s="21" t="inlineStr">
         <is>
           <t>4440069-AS-105667</t>
         </is>
@@ -13293,7 +13362,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J143" s="18" t="n">
+      <c r="J143" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K143" s="4" t="n">
@@ -13304,7 +13373,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M143" s="19" t="inlineStr">
+      <c r="M143" s="21" t="inlineStr">
         <is>
           <t>4440070-AS-105581</t>
         </is>
@@ -13359,7 +13428,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J144" s="18" t="n">
+      <c r="J144" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K144" s="4" t="n">
@@ -13370,7 +13439,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M144" s="19" t="inlineStr">
+      <c r="M144" s="21" t="inlineStr">
         <is>
           <t>4441419-AS-105876</t>
         </is>
@@ -13425,7 +13494,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J145" s="18" t="n">
+      <c r="J145" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K145" s="4" t="n">
@@ -13436,7 +13505,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M145" s="19" t="inlineStr">
+      <c r="M145" s="21" t="inlineStr">
         <is>
           <t>4441420-AS-105890</t>
         </is>
@@ -13491,7 +13560,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J146" s="18" t="n">
+      <c r="J146" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K146" s="4" t="n">
@@ -13502,7 +13571,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M146" s="19" t="inlineStr">
+      <c r="M146" s="21" t="inlineStr">
         <is>
           <t>4449620-AS-106379</t>
         </is>
@@ -13557,7 +13626,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J147" s="18" t="n">
+      <c r="J147" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K147" s="4" t="n">
@@ -13568,7 +13637,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M147" s="19" t="inlineStr">
+      <c r="M147" s="21" t="inlineStr">
         <is>
           <t>4454774-AS-106751</t>
         </is>
@@ -13623,7 +13692,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J148" s="18" t="n">
+      <c r="J148" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K148" s="4" t="n">
@@ -13634,7 +13703,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M148" s="19" t="inlineStr">
+      <c r="M148" s="21" t="inlineStr">
         <is>
           <t>4456204-AS-106912</t>
         </is>
@@ -13689,7 +13758,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J149" s="18" t="n">
+      <c r="J149" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K149" s="4" t="n">
@@ -13700,7 +13769,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M149" s="19" t="inlineStr">
+      <c r="M149" s="21" t="inlineStr">
         <is>
           <t>4456205-AS-106971</t>
         </is>
@@ -13755,7 +13824,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J150" s="18" t="n">
+      <c r="J150" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K150" s="4" t="n">
@@ -13766,7 +13835,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M150" s="19" t="inlineStr">
+      <c r="M150" s="21" t="inlineStr">
         <is>
           <t>4456326-AS-106477</t>
         </is>
@@ -13821,7 +13890,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J151" s="18" t="n">
+      <c r="J151" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K151" s="4" t="n">
@@ -13832,7 +13901,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M151" s="19" t="inlineStr">
+      <c r="M151" s="21" t="inlineStr">
         <is>
           <t>4460094-AS-107180</t>
         </is>
@@ -13887,7 +13956,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J152" s="18" t="n">
+      <c r="J152" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K152" s="4" t="n">
@@ -13898,7 +13967,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M152" s="19" t="inlineStr">
+      <c r="M152" s="21" t="inlineStr">
         <is>
           <t>4469149-AS-107648</t>
         </is>
@@ -13953,7 +14022,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J153" s="18" t="n">
+      <c r="J153" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K153" s="4" t="n">
@@ -13964,7 +14033,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M153" s="19" t="inlineStr">
+      <c r="M153" s="21" t="inlineStr">
         <is>
           <t>4469150-AS-107705</t>
         </is>
@@ -14019,7 +14088,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J154" s="18" t="n">
+      <c r="J154" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K154" s="4" t="n">
@@ -14030,7 +14099,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M154" s="19" t="inlineStr">
+      <c r="M154" s="21" t="inlineStr">
         <is>
           <t>4469151-AS-107615</t>
         </is>
@@ -14085,7 +14154,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J155" s="18" t="n">
+      <c r="J155" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K155" s="4" t="n">
@@ -14096,7 +14165,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M155" s="19" t="inlineStr">
+      <c r="M155" s="21" t="inlineStr">
         <is>
           <t>10001492157742</t>
         </is>
@@ -14151,7 +14220,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J156" s="18" t="n">
+      <c r="J156" s="20" t="n">
         <v>1.1644</v>
       </c>
       <c r="K156" s="4" t="n">
@@ -14162,7 +14231,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M156" s="19" t="inlineStr">
+      <c r="M156" s="21" t="inlineStr">
         <is>
           <t>2026-0028</t>
         </is>
@@ -14217,7 +14286,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J157" s="18" t="n">
+      <c r="J157" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K157" s="4" t="n">
@@ -14228,7 +14297,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M157" s="19" t="inlineStr">
+      <c r="M157" s="21" t="inlineStr">
         <is>
           <t>172168</t>
         </is>
@@ -14283,7 +14352,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J158" s="18" t="n">
+      <c r="J158" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K158" s="4" t="n">
@@ -14294,7 +14363,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M158" s="19" t="inlineStr">
+      <c r="M158" s="21" t="inlineStr">
         <is>
           <t>172169</t>
         </is>
@@ -14349,7 +14418,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J159" s="18" t="n">
+      <c r="J159" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K159" s="4" t="n">
@@ -14360,7 +14429,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M159" s="19" t="inlineStr">
+      <c r="M159" s="21" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
@@ -14415,7 +14484,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J160" s="18" t="n">
+      <c r="J160" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K160" s="4" t="n">
@@ -14426,7 +14495,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M160" s="19" t="inlineStr">
+      <c r="M160" s="21" t="inlineStr">
         <is>
           <t>2329-7934</t>
         </is>
@@ -14481,7 +14550,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J161" s="18" t="n">
+      <c r="J161" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K161" s="4" t="n">
@@ -14492,7 +14561,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M161" s="19" t="inlineStr">
+      <c r="M161" s="21" t="inlineStr">
         <is>
           <t>38249783</t>
         </is>
@@ -14547,7 +14616,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J162" s="18" t="n">
+      <c r="J162" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K162" s="4" t="n">
@@ -14558,7 +14627,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M162" s="19" t="inlineStr">
+      <c r="M162" s="21" t="inlineStr">
         <is>
           <t>38415356</t>
         </is>
@@ -14613,7 +14682,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J163" s="18" t="n">
+      <c r="J163" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K163" s="4" t="n">
@@ -14624,7 +14693,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M163" s="19" t="inlineStr">
+      <c r="M163" s="21" t="inlineStr">
         <is>
           <t>4473263-AS-108173</t>
         </is>
@@ -14679,7 +14748,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J164" s="18" t="n">
+      <c r="J164" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K164" s="4" t="n">
@@ -14690,7 +14759,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M164" s="19" t="inlineStr">
+      <c r="M164" s="21" t="inlineStr">
         <is>
           <t>4473264-AS-108192</t>
         </is>
@@ -14745,7 +14814,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J165" s="18" t="n">
+      <c r="J165" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K165" s="4" t="n">
@@ -14756,7 +14825,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M165" s="19" t="inlineStr">
+      <c r="M165" s="21" t="inlineStr">
         <is>
           <t>4473265-AS-108268</t>
         </is>
@@ -14811,7 +14880,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J166" s="18" t="n">
+      <c r="J166" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K166" s="4" t="n">
@@ -14822,7 +14891,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M166" s="19" t="inlineStr">
+      <c r="M166" s="21" t="inlineStr">
         <is>
           <t>4473266-AS-108012</t>
         </is>
@@ -14877,7 +14946,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J167" s="18" t="n">
+      <c r="J167" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K167" s="4" t="n">
@@ -14888,7 +14957,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M167" s="19" t="inlineStr">
+      <c r="M167" s="21" t="inlineStr">
         <is>
           <t>4476206-AS-108439</t>
         </is>
@@ -14943,7 +15012,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J168" s="18" t="n">
+      <c r="J168" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K168" s="4" t="n">
@@ -14954,7 +15023,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M168" s="19" t="inlineStr">
+      <c r="M168" s="21" t="inlineStr">
         <is>
           <t>4478432-AS-108770</t>
         </is>
@@ -15009,7 +15078,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J169" s="18" t="n">
+      <c r="J169" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K169" s="4" t="n">
@@ -15020,7 +15089,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M169" s="19" t="inlineStr">
+      <c r="M169" s="21" t="inlineStr">
         <is>
           <t>4478433-AS-108794</t>
         </is>
@@ -15075,7 +15144,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J170" s="18" t="n">
+      <c r="J170" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K170" s="4" t="n">
@@ -15086,7 +15155,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M170" s="19" t="inlineStr">
+      <c r="M170" s="21" t="inlineStr">
         <is>
           <t>4478436-AS-108633</t>
         </is>
@@ -15141,7 +15210,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J171" s="18" t="n">
+      <c r="J171" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K171" s="4" t="n">
@@ -15152,7 +15221,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M171" s="19" t="inlineStr">
+      <c r="M171" s="21" t="inlineStr">
         <is>
           <t>4478438-AS-108725</t>
         </is>
@@ -15207,7 +15276,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J172" s="18" t="n">
+      <c r="J172" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K172" s="4" t="n">
@@ -15218,7 +15287,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M172" s="19" t="inlineStr">
+      <c r="M172" s="21" t="inlineStr">
         <is>
           <t>4478674-AS-108419</t>
         </is>
@@ -15273,7 +15342,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J173" s="18" t="n">
+      <c r="J173" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K173" s="4" t="n">
@@ -15284,7 +15353,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M173" s="19" t="inlineStr">
+      <c r="M173" s="21" t="inlineStr">
         <is>
           <t>4479450-AS-108886</t>
         </is>
@@ -15339,7 +15408,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J174" s="18" t="n">
+      <c r="J174" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K174" s="4" t="n">
@@ -15350,7 +15419,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M174" s="19" t="inlineStr">
+      <c r="M174" s="21" t="inlineStr">
         <is>
           <t>4480313-AS-108991</t>
         </is>
@@ -15405,7 +15474,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J175" s="18" t="n">
+      <c r="J175" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K175" s="4" t="n">
@@ -15416,7 +15485,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M175" s="19" t="inlineStr">
+      <c r="M175" s="21" t="inlineStr">
         <is>
           <t>4481152-AS-109059</t>
         </is>
@@ -15471,7 +15540,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J176" s="18" t="n">
+      <c r="J176" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K176" s="4" t="n">
@@ -15482,7 +15551,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M176" s="19" t="inlineStr">
+      <c r="M176" s="21" t="inlineStr">
         <is>
           <t>4484741-AS-109219</t>
         </is>
@@ -15537,7 +15606,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J177" s="18" t="n">
+      <c r="J177" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K177" s="4" t="n">
@@ -15548,7 +15617,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M177" s="19" t="inlineStr">
+      <c r="M177" s="21" t="inlineStr">
         <is>
           <t>4484745-AS-109054</t>
         </is>
@@ -15603,7 +15672,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J178" s="18" t="n">
+      <c r="J178" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K178" s="4" t="n">
@@ -15614,7 +15683,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M178" s="19" t="inlineStr">
+      <c r="M178" s="21" t="inlineStr">
         <is>
           <t>4487374-AS-108398</t>
         </is>
@@ -15669,7 +15738,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J179" s="18" t="n">
+      <c r="J179" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K179" s="4" t="n">
@@ -15680,7 +15749,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M179" s="19" t="inlineStr">
+      <c r="M179" s="21" t="inlineStr">
         <is>
           <t>4489467-AS-109600</t>
         </is>
@@ -15735,7 +15804,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J180" s="18" t="n">
+      <c r="J180" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K180" s="4" t="n">
@@ -15746,7 +15815,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M180" s="19" t="inlineStr">
+      <c r="M180" s="21" t="inlineStr">
         <is>
           <t>4489492-AS-109897</t>
         </is>
@@ -15801,7 +15870,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J181" s="18" t="n">
+      <c r="J181" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K181" s="4" t="n">
@@ -15812,7 +15881,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M181" s="19" t="inlineStr">
+      <c r="M181" s="21" t="inlineStr">
         <is>
           <t>4489493-AS-109730</t>
         </is>
@@ -15867,7 +15936,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J182" s="18" t="n">
+      <c r="J182" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K182" s="4" t="n">
@@ -15878,7 +15947,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M182" s="19" t="inlineStr">
+      <c r="M182" s="21" t="inlineStr">
         <is>
           <t>4490302-AS-109750</t>
         </is>
@@ -15933,7 +16002,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J183" s="18" t="n">
+      <c r="J183" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K183" s="4" t="n">
@@ -15944,7 +16013,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M183" s="19" t="inlineStr">
+      <c r="M183" s="21" t="inlineStr">
         <is>
           <t>4492194-AS-109976</t>
         </is>
@@ -15999,7 +16068,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J184" s="18" t="n">
+      <c r="J184" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K184" s="4" t="n">
@@ -16010,7 +16079,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M184" s="19" t="inlineStr">
+      <c r="M184" s="21" t="inlineStr">
         <is>
           <t>4492195-AS-110005</t>
         </is>
@@ -16065,7 +16134,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J185" s="18" t="n">
+      <c r="J185" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K185" s="4" t="n">
@@ -16076,7 +16145,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M185" s="19" t="inlineStr">
+      <c r="M185" s="21" t="inlineStr">
         <is>
           <t>4493889-AS-110166</t>
         </is>
@@ -16131,7 +16200,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J186" s="18" t="n">
+      <c r="J186" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K186" s="4" t="n">
@@ -16142,7 +16211,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M186" s="19" t="inlineStr">
+      <c r="M186" s="21" t="inlineStr">
         <is>
           <t>4493890-AS-110181</t>
         </is>
@@ -16197,7 +16266,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J187" s="18" t="n">
+      <c r="J187" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K187" s="4" t="n">
@@ -16208,7 +16277,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M187" s="19" t="inlineStr">
+      <c r="M187" s="21" t="inlineStr">
         <is>
           <t>4494780-AS-110429</t>
         </is>
@@ -16263,7 +16332,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J188" s="18" t="n">
+      <c r="J188" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K188" s="4" t="n">
@@ -16274,7 +16343,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M188" s="19" t="inlineStr">
+      <c r="M188" s="21" t="inlineStr">
         <is>
           <t>10001500801887</t>
         </is>
@@ -16329,7 +16398,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J189" s="18" t="n">
+      <c r="J189" s="20" t="n">
         <v>1.1394</v>
       </c>
       <c r="K189" s="4" t="n">
@@ -16340,7 +16409,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M189" s="19" t="inlineStr">
+      <c r="M189" s="21" t="inlineStr">
         <is>
           <t>2026-0030</t>
         </is>
@@ -16395,7 +16464,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J190" s="18" t="n">
+      <c r="J190" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K190" s="4" t="n">
@@ -16406,7 +16475,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M190" s="19" t="inlineStr">
+      <c r="M190" s="21" t="inlineStr">
         <is>
           <t>172285</t>
         </is>
@@ -16461,7 +16530,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J191" s="18" t="n">
+      <c r="J191" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K191" s="4" t="n">
@@ -16472,7 +16541,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M191" s="19" t="inlineStr">
+      <c r="M191" s="21" t="inlineStr">
         <is>
           <t>172285</t>
         </is>
@@ -16527,7 +16596,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="J192" s="18" t="n">
+      <c r="J192" s="20" t="n">
         <v>1</v>
       </c>
       <c r="K192" s="4" t="n">
@@ -16538,7 +16607,7 @@
           <t>documents</t>
         </is>
       </c>
-      <c r="M192" s="19" t="inlineStr">
+      <c r="M192" s="21" t="inlineStr">
         <is>
           <t>1323</t>
         </is>
@@ -16768,54 +16837,54 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>amount_original</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="H2" s="17" t="inlineStr">
+      <c r="H2" s="19" t="inlineStr">
         <is>
           <t>amount_reporting</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
+      <c r="I2" s="19" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -16850,7 +16919,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G3" s="18" t="n">
+      <c r="G3" s="20" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="4" t="n">
@@ -16891,7 +16960,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="20" t="n">
         <v>1</v>
       </c>
       <c r="H4" s="4" t="n">
@@ -16932,7 +17001,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="20" t="n">
         <v>1</v>
       </c>
       <c r="H5" s="4" t="n">
@@ -16973,7 +17042,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="20" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="4" t="n">
@@ -17014,7 +17083,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="20" t="n">
         <v>1</v>
       </c>
       <c r="H7" s="4" t="n">
@@ -17055,7 +17124,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="20" t="n">
         <v>1</v>
       </c>
       <c r="H8" s="4" t="n">
@@ -17084,7 +17153,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>76.05</v>
+        <v>354.62</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -17096,11 +17165,11 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="20" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>76.05</v>
+        <v>354.62</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -17135,44 +17204,44 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>yyyymm</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>rate_date</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>currency_original</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>reporting_currency</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>reference_rate</t>
         </is>
       </c>
-      <c r="F2" s="17" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>fx_rate</t>
         </is>
       </c>
-      <c r="G2" s="17" t="inlineStr">
+      <c r="G2" s="19" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -17199,10 +17268,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E3" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="18" t="n">
+      <c r="E3" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="20" t="n">
         <v>1.1919</v>
       </c>
       <c r="G3" t="inlineStr">
@@ -17232,10 +17301,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E4" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="18" t="n">
+      <c r="E4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G4" t="inlineStr">
@@ -17265,10 +17334,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="18" t="n">
+      <c r="E5" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="20" t="n">
         <v>1.1805</v>
       </c>
       <c r="G5" t="inlineStr">
@@ -17298,10 +17367,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="18" t="n">
+      <c r="E6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -17331,10 +17400,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="18" t="n">
+      <c r="E7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="20" t="n">
         <v>1.1498</v>
       </c>
       <c r="G7" t="inlineStr">
@@ -17364,10 +17433,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" s="18" t="n">
+      <c r="E8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -17397,10 +17466,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E9" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="18" t="n">
+      <c r="E9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="20" t="n">
         <v>1.1702</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -17430,10 +17499,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="18" t="n">
+      <c r="E10" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
@@ -17463,10 +17532,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E11" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="18" t="n">
+      <c r="E11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="20" t="n">
         <v>1.1644</v>
       </c>
       <c r="G11" t="inlineStr">
@@ -17496,10 +17565,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E12" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="18" t="n">
+      <c r="E12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -17529,10 +17598,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E13" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="18" t="n">
+      <c r="E13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="20" t="n">
         <v>1.1394</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -17562,10 +17631,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E14" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="18" t="n">
+      <c r="E14" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
@@ -17595,10 +17664,10 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="E15" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="18" t="n">
+      <c r="E15" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="20" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
@@ -17632,34 +17701,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="12" customHeight="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>&lt;- Volver a P&amp;G-INC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>supplier_code</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>supplier_name</t>
         </is>
       </c>
-      <c r="C2" s="17" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>current_folder</t>
         </is>
       </c>
-      <c r="D2" s="17" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>destination_path</t>
         </is>
       </c>
-      <c r="E2" s="17" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -17998,7 +18067,7 @@
       </c>
     </row>
     <row r="2" ht="12" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>Nº Facturas INC 2026</t>
         </is>
@@ -18072,151 +18141,151 @@
       </c>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Turnover</t>
         </is>
       </c>
-      <c r="B4" s="22" t="n"/>
-      <c r="C4" s="22" t="n"/>
-      <c r="D4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="22" t="n">
+      <c r="B4" s="24" t="n"/>
+      <c r="C4" s="24" t="n"/>
+      <c r="D4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="Q4" s="22" t="n"/>
+      <c r="Q4" s="24" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="23" t="n"/>
-      <c r="B5" s="24" t="inlineStr">
+      <c r="A5" s="25" t="n"/>
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>Product sales</t>
         </is>
       </c>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="23" t="n">
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="Q5" s="23" t="n"/>
+      <c r="Q5" s="25" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="25" t="n"/>
+      <c r="A6" s="27" t="n"/>
+      <c r="B6" s="27" t="n"/>
       <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="25" t="n">
+      <c r="D6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="Q6" s="25" t="n"/>
+      <c r="Q6" s="27" t="n"/>
     </row>
     <row r="7" ht="12" customHeight="1">
       <c r="C7" t="inlineStr">
@@ -18265,250 +18334,250 @@
       </c>
     </row>
     <row r="8" ht="12" customHeight="1">
-      <c r="A8" s="23" t="n"/>
-      <c r="B8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="n"/>
+      <c r="B8" s="26" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="C8" s="23" t="n"/>
-      <c r="D8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="23" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="25" t="n"/>
     </row>
     <row r="9" ht="12" customHeight="1">
-      <c r="A9" s="25" t="n"/>
+      <c r="A9" s="27" t="n"/>
       <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Uncategorized income</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n"/>
-      <c r="D9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="25" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="27" t="n"/>
     </row>
     <row r="10" ht="12" customHeight="1"/>
     <row r="11" ht="12" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n">
         <v>19</v>
       </c>
-      <c r="E11" s="22" t="n">
+      <c r="E11" s="24" t="n">
         <v>29</v>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="24" t="n">
         <v>45</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="24" t="n">
         <v>42</v>
       </c>
-      <c r="H11" s="22" t="n">
+      <c r="H11" s="24" t="n">
         <v>26</v>
       </c>
-      <c r="I11" s="22" t="n">
+      <c r="I11" s="24" t="n">
         <v>34</v>
       </c>
-      <c r="J11" s="22" t="n">
+      <c r="J11" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="K11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="22" t="n">
+      <c r="K11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="24" t="n">
         <v>197</v>
       </c>
-      <c r="Q11" s="22" t="n"/>
+      <c r="Q11" s="24" t="n"/>
     </row>
     <row r="12" ht="12" customHeight="1">
-      <c r="A12" s="23" t="n"/>
-      <c r="B12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="26" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n">
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="25" t="n">
         <v>21</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="25" t="n">
         <v>31</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="25" t="n">
         <v>33</v>
       </c>
-      <c r="H12" s="23" t="n">
+      <c r="H12" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="I12" s="23" t="n">
+      <c r="I12" s="25" t="n">
         <v>28</v>
       </c>
-      <c r="J12" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="23" t="n">
+      <c r="J12" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="Q12" s="23" t="n"/>
+      <c r="Q12" s="25" t="n"/>
     </row>
     <row r="13" ht="12" customHeight="1">
-      <c r="A13" s="25" t="n"/>
-      <c r="B13" s="25" t="n"/>
+      <c r="A13" s="27" t="n"/>
+      <c r="B13" s="27" t="n"/>
       <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Manufacturing</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E13" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="27" t="n">
         <v>29</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="27" t="n">
         <v>31</v>
       </c>
-      <c r="H13" s="25" t="n">
+      <c r="H13" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="I13" s="25" t="n">
+      <c r="I13" s="27" t="n">
         <v>26</v>
       </c>
-      <c r="J13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="25" t="n">
+      <c r="J13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="27" t="n">
         <v>127</v>
       </c>
-      <c r="Q13" s="25" t="n"/>
+      <c r="Q13" s="27" t="n"/>
     </row>
     <row r="14" ht="12" customHeight="1">
       <c r="C14" t="inlineStr">
@@ -18534,7 +18603,7 @@
       <c r="I14" t="n">
         <v>25</v>
       </c>
-      <c r="J14" s="26" t="n">
+      <c r="J14" s="28" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
@@ -18580,7 +18649,7 @@
       <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" s="26" t="n">
+      <c r="J15" s="28" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
@@ -18603,53 +18672,53 @@
       </c>
     </row>
     <row r="16" ht="12" customHeight="1">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="25" t="n"/>
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="27" t="n"/>
       <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Logistics</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="25" t="n">
+      <c r="D16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="Q16" s="25" t="n"/>
+      <c r="Q16" s="27" t="n"/>
     </row>
     <row r="17" ht="12" customHeight="1">
       <c r="C17" t="inlineStr">
@@ -18675,7 +18744,7 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" s="26" t="n">
+      <c r="J17" s="28" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
@@ -18698,53 +18767,53 @@
       </c>
     </row>
     <row r="18" ht="12" customHeight="1">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="25" t="n"/>
+      <c r="A18" s="27" t="n"/>
+      <c r="B18" s="27" t="n"/>
       <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Payment fees</t>
         </is>
       </c>
-      <c r="D18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" s="25" t="n">
+      <c r="D18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="Q18" s="25" t="n"/>
+      <c r="Q18" s="27" t="n"/>
     </row>
     <row r="19" ht="12" customHeight="1">
       <c r="C19" t="inlineStr">
@@ -18794,102 +18863,102 @@
     </row>
     <row r="20" ht="12" customHeight="1"/>
     <row r="21" ht="12" customHeight="1">
-      <c r="A21" s="23" t="n"/>
-      <c r="B21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="26" t="inlineStr">
         <is>
           <t>Opex</t>
         </is>
       </c>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n">
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="E21" s="23" t="n">
+      <c r="E21" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="23" t="n">
+      <c r="F21" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="G21" s="23" t="n">
+      <c r="G21" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="H21" s="23" t="n">
+      <c r="H21" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="23" t="n">
+      <c r="I21" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="J21" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="23" t="n">
+      <c r="J21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="25" t="n">
         <v>57</v>
       </c>
-      <c r="Q21" s="23" t="n"/>
+      <c r="Q21" s="25" t="n"/>
     </row>
     <row r="22" ht="12" customHeight="1">
-      <c r="A22" s="25" t="n"/>
-      <c r="B22" s="25" t="n"/>
+      <c r="A22" s="27" t="n"/>
+      <c r="B22" s="27" t="n"/>
       <c r="C22" s="9" t="inlineStr">
         <is>
           <t>Shared services</t>
         </is>
       </c>
-      <c r="D22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I22" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="25" t="n">
+      <c r="D22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="Q22" s="25" t="n"/>
+      <c r="Q22" s="27" t="n"/>
     </row>
     <row r="23" ht="12" customHeight="1">
       <c r="C23" t="inlineStr">
@@ -18915,7 +18984,7 @@
       <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" s="26" t="n">
+      <c r="J23" s="28" t="n">
         <v>0</v>
       </c>
       <c r="K23" t="n">
@@ -18938,53 +19007,53 @@
       </c>
     </row>
     <row r="24" ht="12" customHeight="1">
-      <c r="A24" s="25" t="n"/>
-      <c r="B24" s="25" t="n"/>
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="27" t="n"/>
       <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Administration</t>
         </is>
       </c>
-      <c r="D24" s="25" t="n">
+      <c r="D24" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E24" s="25" t="n">
+      <c r="E24" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="F24" s="25" t="n">
+      <c r="F24" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="G24" s="25" t="n">
+      <c r="G24" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="H24" s="25" t="n">
+      <c r="H24" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="I24" s="25" t="n">
+      <c r="I24" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="J24" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="25" t="n">
+      <c r="J24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="27" t="n">
         <v>51</v>
       </c>
-      <c r="Q24" s="25" t="n"/>
+      <c r="Q24" s="27" t="n"/>
     </row>
     <row r="25" ht="12" customHeight="1">
       <c r="C25" t="inlineStr">
@@ -19102,7 +19171,7 @@
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="26" t="n">
+      <c r="J27" s="28" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
@@ -19148,7 +19217,7 @@
       <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="26" t="n">
+      <c r="J28" s="28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
@@ -19194,7 +19263,7 @@
       <c r="I29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" s="26" t="n">
+      <c r="J29" s="28" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
@@ -19263,53 +19332,53 @@
       </c>
     </row>
     <row r="31" ht="12" customHeight="1">
-      <c r="A31" s="25" t="n"/>
-      <c r="B31" s="25" t="n"/>
+      <c r="A31" s="27" t="n"/>
+      <c r="B31" s="27" t="n"/>
       <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="D31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="25" t="n"/>
+      <c r="D31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="27" t="n"/>
     </row>
     <row r="32" ht="12" customHeight="1">
       <c r="C32" t="inlineStr">
@@ -19358,102 +19427,102 @@
       </c>
     </row>
     <row r="33" ht="12" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="25" t="n"/>
+      <c r="A33" s="27" t="n"/>
+      <c r="B33" s="27" t="n"/>
       <c r="C33" s="9" t="inlineStr">
         <is>
           <t>Uncategorized Expenses</t>
         </is>
       </c>
-      <c r="D33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="25" t="n"/>
+      <c r="D33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="27" t="n"/>
     </row>
     <row r="34" ht="12" customHeight="1">
-      <c r="A34" s="25" t="n"/>
+      <c r="A34" s="27" t="n"/>
       <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Currency Adjustment</t>
         </is>
       </c>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="25" t="n"/>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/output/spreadsheet/pyg_inc_2026.xlsx
+++ b/output/spreadsheet/pyg_inc_2026.xlsx
@@ -709,7 +709,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shopify daily average | Actualizado: 31/07/2026 09:48 h</t>
+          <t>Shopify daily average | Actualizado: 31/07/2026 12:25 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -955,7 +955,7 @@
         </is>
       </c>
     </row>
-    <row r="7" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+    <row r="7" ht="12" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t xml:space="preserve">      US</t>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="12" customHeight="1">
+    <row r="8" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">        avg/day</t>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31T07:48:06Z</t>
+          <t>2026-07-31T10:25:42Z</t>
         </is>
       </c>
     </row>
